--- a/dist/data/products.xlsx
+++ b/dist/data/products.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:L121"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,34 +442,34 @@
         <v>GS-1001</v>
       </c>
       <c r="B2" t="str">
-        <v>Royal Aged Basmati Rice (XXL Long Grain)</v>
+        <v>Aachi Chilli Powder</v>
       </c>
       <c r="C2" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Aachi Masala &amp; Podi</v>
       </c>
       <c r="D2">
-        <v>185</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>230</v>
+        <v>45</v>
       </c>
       <c r="F2" t="str">
-        <v>1 kg</v>
+        <v>100 g</v>
       </c>
       <c r="G2">
         <v>4.9</v>
       </c>
       <c r="H2">
-        <v>342</v>
+        <v>102</v>
       </c>
       <c r="I2" t="str">
-        <v>https://images.unsplash.com/photo-1586201375761-83865001e31c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/001_Aachi_Chilli_Powder.jpg</v>
       </c>
       <c r="J2" t="str">
-        <v>2-year aged Himalayan foothill Basmati with delicate fragrant aroma and elongated fluffy grains that double in length when cooked.</v>
+        <v>Pure spicy red chilli powder sun-dried and ground to perfection.</v>
       </c>
       <c r="K2" t="str">
-        <v>Origin: Dehradun Valley. Aged: 24 Months. Non-GMO, pesticide-free harvest. Ideal for royal biryanis and festive pulao.</v>
+        <v>100% Guntur Red Chillies. No artificial colours or preservatives.</v>
       </c>
       <c r="L2" t="str">
         <v>In Stock</v>
@@ -480,34 +480,34 @@
         <v>GS-1002</v>
       </c>
       <c r="B3" t="str">
-        <v>Organic Traditional Sona Masoori Raw Rice</v>
+        <v>Aachi Turmeric Powder</v>
       </c>
       <c r="C3" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Aachi Masala &amp; Podi</v>
       </c>
       <c r="D3">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="F3" t="str">
-        <v>1 kg</v>
+        <v>100 g</v>
       </c>
       <c r="G3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H3">
-        <v>289</v>
+        <v>119</v>
       </c>
       <c r="I3" t="str">
-        <v>https://images.unsplash.com/photo-1536304993881-ff6e9eefa2a6?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/002_Aachi_Turmeric_Powder.jpg</v>
       </c>
       <c r="J3" t="str">
-        <v>Lightweight, aromatic medium-grain rice grown organically along the Tungabhadra river basin, effortlessly easy to digest.</v>
+        <v>Golden Erode turmeric powder rich in natural curcumin.</v>
       </c>
       <c r="K3" t="str">
-        <v>Origin: Tungabhadra Basin. Naturally unpolished, rich in essential dietary fiber and gentle on digestion.</v>
+        <v>High-curcumin pure turmeric root. Traditional Salem/Erode harvest.</v>
       </c>
       <c r="L3" t="str">
         <v>In Stock</v>
@@ -518,34 +518,34 @@
         <v>GS-1003</v>
       </c>
       <c r="B4" t="str">
-        <v>Traditional Single-Boiled Ponni Rice</v>
+        <v>Aachi Coriander Powder</v>
       </c>
       <c r="C4" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Aachi Masala &amp; Podi</v>
       </c>
       <c r="D4">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="F4" t="str">
-        <v>1 kg</v>
+        <v>100 g</v>
       </c>
       <c r="G4">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H4">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="I4" t="str">
-        <v>https://images.unsplash.com/photo-1516684732162-798a0062be99?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/003_Aachi_Coriander_Powder.jpg</v>
       </c>
       <c r="J4" t="str">
-        <v>Steamed once in copper vats to lock in nutrition. Firm, non-sticky texture preferred for authentic South Indian lunches.</v>
+        <v>Fragrant coriander powder roasted and ground for authentic gravy flavour.</v>
       </c>
       <c r="K4" t="str">
-        <v>Origin: Kaveri Delta, Thanjavur. Parboiled single steam method. Excellent glycemic balance.</v>
+        <v>Selected green coriander seeds. Cold-ground aroma lock.</v>
       </c>
       <c r="L4" t="str">
         <v>In Stock</v>
@@ -556,34 +556,34 @@
         <v>GS-1004</v>
       </c>
       <c r="B5" t="str">
-        <v>Ancient Brown Foxtail Millet (Thinai)</v>
+        <v>Aachi Sambar Powder</v>
       </c>
       <c r="C5" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Aachi Masala &amp; Podi</v>
       </c>
       <c r="D5">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="E5">
-        <v>145</v>
+        <v>50</v>
       </c>
       <c r="F5" t="str">
-        <v>500 g</v>
+        <v>100 g</v>
       </c>
       <c r="G5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H5">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="I5" t="str">
-        <v>https://images.unsplash.com/photo-1574323347407-f5e1ad6d020b?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/004_Aachi_Sambar_Powder.jpg</v>
       </c>
       <c r="J5" t="str">
-        <v>Supergrain rich in iron, zinc, and slow-release complex carbs. Naturally gluten-free and diabetic friendly.</v>
+        <v>Authentic South Indian sambar masala powder with traditional spices and lentils.</v>
       </c>
       <c r="K5" t="str">
-        <v>Origin: Dharmapuri rain-fed farms. 100% whole grain unpolished millet. High dietary fiber (12g/100g).</v>
+        <v>Heritage blend of coriander, red chilli, fenugreek, toor dal, and asafoetida.</v>
       </c>
       <c r="L5" t="str">
         <v>In Stock</v>
@@ -594,34 +594,34 @@
         <v>GS-1005</v>
       </c>
       <c r="B6" t="str">
-        <v>Stone-Ground Whole Wheat Sharbati Atta</v>
+        <v>Aachi Rasam Powder</v>
       </c>
       <c r="C6" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Aachi Masala &amp; Podi</v>
       </c>
       <c r="D6">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c r="E6">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="F6" t="str">
-        <v>5 kg</v>
+        <v>100 g</v>
       </c>
       <c r="G6">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H6">
-        <v>512</v>
+        <v>170</v>
       </c>
       <c r="I6" t="str">
-        <v>https://images.unsplash.com/photo-1509440159596-0249088772ff?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/005_Aachi_Rasam_Powder.jpg</v>
       </c>
       <c r="J6" t="str">
-        <v>Ground on slow-spinning natural stone chakki to retain germ and bran. Makes exceptionally soft, golden, puffed rotis.</v>
+        <v>Zesty aromatic rasam powder for steaming piping hot South Indian rasam.</v>
       </c>
       <c r="K6" t="str">
-        <v>Origin: Sehore, Madhya Pradesh. 100% MP Sharbati whole grain. Cold-milled under 40°C to preserve natural vitamins.</v>
+        <v>Rich in black pepper, cumin, coriander, and curry leaf essence.</v>
       </c>
       <c r="L6" t="str">
         <v>In Stock</v>
@@ -632,34 +632,34 @@
         <v>GS-1006</v>
       </c>
       <c r="B7" t="str">
-        <v>Organic Red Rice (Kattuyanam)</v>
+        <v>Aachi Chicken Masala</v>
       </c>
       <c r="C7" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Aachi Masala &amp; Podi</v>
       </c>
       <c r="D7">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="E7">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="F7" t="str">
-        <v>1 kg</v>
+        <v>100 g</v>
       </c>
       <c r="G7">
         <v>4.8</v>
       </c>
       <c r="H7">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="I7" t="str">
-        <v>https://images.unsplash.com/photo-1546069901-ba9599a7e63c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/006_Aachi_Chicken_Masala.jpg</v>
       </c>
       <c r="J7" t="str">
-        <v>Rare indigenous heritage red rice revered in Siddha medicine for building stamina and vitality.</v>
+        <v>Special aromatic spice blend for restaurant-style Chicken curry, fry, and sukka.</v>
       </c>
       <c r="K7" t="str">
-        <v>Origin: Pudukkottai wild agro-forests. Anthocyanin-rich bran layer with dense antioxidant profile.</v>
+        <v>Contains star anise, black pepper, cloves, cinnamon, and roasted spices.</v>
       </c>
       <c r="L7" t="str">
         <v>In Stock</v>
@@ -670,34 +670,34 @@
         <v>GS-1007</v>
       </c>
       <c r="B8" t="str">
-        <v>Whole Finger Millet Flour (Ragi Atta)</v>
+        <v>Aachi Mutton Masala</v>
       </c>
       <c r="C8" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Aachi Masala &amp; Podi</v>
       </c>
       <c r="D8">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="E8">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="F8" t="str">
-        <v>1 kg</v>
+        <v>100 g</v>
       </c>
       <c r="G8">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H8">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="I8" t="str">
-        <v>https://images.unsplash.com/photo-1586201375761-83865001e31c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/007_Aachi_Mutton_Masala.jpg</v>
       </c>
       <c r="J8" t="str">
-        <v>Naturally sprouted and stone-ground ragi loaded with ten times the calcium of standard white rice or milk.</v>
+        <v>Rich flavourful spice blend for succulent, tender mutton kuzhambu and chukka.</v>
       </c>
       <c r="K8" t="str">
-        <v>Calcium powerhouse: 344mg/100g. Recommended for growing children, elders, and nutrient-dense rotis/porridge.</v>
+        <v>Formulated with rustic stone-ground spices for deep aroma.</v>
       </c>
       <c r="L8" t="str">
         <v>In Stock</v>
@@ -708,34 +708,34 @@
         <v>GS-1008</v>
       </c>
       <c r="B9" t="str">
-        <v>Pearl Millet (Kambu / Bajra Grains)</v>
+        <v>Aachi Garam Masala</v>
       </c>
       <c r="C9" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Aachi Masala &amp; Podi</v>
       </c>
       <c r="D9">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F9" t="str">
-        <v>1 kg</v>
+        <v>100 g</v>
       </c>
       <c r="G9">
         <v>4.7</v>
       </c>
       <c r="H9">
-        <v>92</v>
+        <v>221</v>
       </c>
       <c r="I9" t="str">
-        <v>https://images.unsplash.com/photo-1574323347407-f5e1ad6d020b?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/008_Aachi_Garam_Masala.jpg</v>
       </c>
       <c r="J9" t="str">
-        <v>Hearty drought-resistant grain revered for summer cooling porridges and hearty winter flatbreads.</v>
+        <v>Finest royal warm spices blend to enhance North &amp; South Indian dishes.</v>
       </c>
       <c r="K9" t="str">
-        <v>Sourced directly from native farmers in Theni. Rich in magnesium, potassium, and amino acids.</v>
+        <v>Cardamom, mace, cinnamon, cloves, bay leaf, and nutmeg blend.</v>
       </c>
       <c r="L9" t="str">
         <v>In Stock</v>
@@ -746,34 +746,34 @@
         <v>GS-1009</v>
       </c>
       <c r="B10" t="str">
-        <v>Little Millet (Samai Raw)</v>
+        <v>Aachi Pepper Powder</v>
       </c>
       <c r="C10" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Aachi Masala &amp; Podi</v>
       </c>
       <c r="D10">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="E10">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="F10" t="str">
-        <v>500 g</v>
+        <v>100 g</v>
       </c>
       <c r="G10">
         <v>4.8</v>
       </c>
       <c r="H10">
-        <v>76</v>
+        <v>238</v>
       </c>
       <c r="I10" t="str">
-        <v>https://images.unsplash.com/photo-1536304993881-ff6e9eefa2a6?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/009_Aachi_Pepper_Powder.jpg</v>
       </c>
       <c r="J10" t="str">
-        <v>Delicate small golden grains with mild nutty taste, cooks fast like rice for wholesome daily meals.</v>
+        <v>Freshly ground Malabar black pepper powder with intense punch and heat.</v>
       </c>
       <c r="K10" t="str">
-        <v>Zero chemical polish. High in B-vitamins and iron. Perfect substitute for table rice.</v>
+        <v>100% pure black peppercorns from Western Ghats. Great for health and soups.</v>
       </c>
       <c r="L10" t="str">
         <v>In Stock</v>
@@ -784,34 +784,34 @@
         <v>GS-1010</v>
       </c>
       <c r="B11" t="str">
-        <v>Kodo Millet (Varagu)</v>
+        <v>Aachi Biryani Masala</v>
       </c>
       <c r="C11" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Aachi Masala &amp; Podi</v>
       </c>
       <c r="D11">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="E11">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="F11" t="str">
-        <v>500 g</v>
+        <v>100 g</v>
       </c>
       <c r="G11">
         <v>4.8</v>
       </c>
       <c r="H11">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="I11" t="str">
-        <v>https://images.unsplash.com/photo-1516684732162-798a0062be99?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/010_Aachi_Biryani_Masala.jpg</v>
       </c>
       <c r="J11" t="str">
-        <v>Ancient grain high in polyphenols and antioxidants, traditionally prescribed for gut health and stamina.</v>
+        <v>Chef's secret recipe spice mix for rich, aromatic Ambur and Chettinad biryani.</v>
       </c>
       <c r="K11" t="str">
-        <v>Origin: Salem hill tracts. Hand-dehulled to preserve outer nutritious aleurone layer.</v>
+        <v>Blended with shahi jeera, mace, nutmeg, cardamom, and aromatic bay leaves.</v>
       </c>
       <c r="L11" t="str">
         <v>In Stock</v>
@@ -822,34 +822,34 @@
         <v>GS-1011</v>
       </c>
       <c r="B12" t="str">
-        <v>Organic Rolled Jumbo Oats</v>
+        <v>Tea Dust</v>
       </c>
       <c r="C12" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Tea &amp; Coffee</v>
       </c>
       <c r="D12">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="E12">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="F12" t="str">
-        <v>1 kg</v>
+        <v>500 g</v>
       </c>
       <c r="G12">
         <v>4.9</v>
       </c>
       <c r="H12">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="I12" t="str">
-        <v>https://images.unsplash.com/photo-1517093708149-a93165b6823d?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/011_Tea_Dust.jpg</v>
       </c>
       <c r="J12" t="str">
-        <v>Thick-cut, whole grain rolled oats delivering rich texture and heart-healthy soluble beta-glucan.</v>
+        <v>Strong hotel-style tea dust delivering rich dark decoction and brisk flavor.</v>
       </c>
       <c r="K12" t="str">
-        <v>100% wholegrain. Zero preservatives, zero additives. Great for warm oatmeal, overnight bowls, or baking.</v>
+        <v>Fine CTC tea dust sourced from Nilgiri hill plantations.</v>
       </c>
       <c r="L12" t="str">
         <v>In Stock</v>
@@ -860,16 +860,16 @@
         <v>GS-1012</v>
       </c>
       <c r="B13" t="str">
-        <v>Barnyard Millet (Kuthiraivali)</v>
+        <v>3 Roses Tea</v>
       </c>
       <c r="C13" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Tea &amp; Coffee</v>
       </c>
       <c r="D13">
-        <v>125</v>
+        <v>340</v>
       </c>
       <c r="E13">
-        <v>150</v>
+        <v>390</v>
       </c>
       <c r="F13" t="str">
         <v>500 g</v>
@@ -878,16 +878,16 @@
         <v>4.7</v>
       </c>
       <c r="H13">
-        <v>84</v>
+        <v>289</v>
       </c>
       <c r="I13" t="str">
-        <v>https://images.unsplash.com/photo-1574323347407-f5e1ad6d020b?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/012_3_Roses_Tea.jpg</v>
       </c>
       <c r="J13" t="str">
-        <v>High in digestible protein and lowest in carbohydrate content among all cereal grains.</v>
+        <v>Rich colour and exquisite aroma tea blended with selected fresh tea leaves.</v>
       </c>
       <c r="K13" t="str">
-        <v>Naturally gluten-free. Fast-cooking grain ideal for nutritious khichdi, idli batter, and upma.</v>
+        <v>Brooke Bond 3 Roses strong CTC leaf tea with signature taste.</v>
       </c>
       <c r="L13" t="str">
         <v>In Stock</v>
@@ -898,34 +898,34 @@
         <v>GS-1013</v>
       </c>
       <c r="B14" t="str">
-        <v>Unpolished Organic Toor Dal (Pigeon Peas)</v>
+        <v>Tata Tea</v>
       </c>
       <c r="C14" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Tea &amp; Coffee</v>
       </c>
       <c r="D14">
-        <v>165</v>
+        <v>290</v>
       </c>
       <c r="E14">
-        <v>195</v>
+        <v>330</v>
       </c>
       <c r="F14" t="str">
-        <v>1 kg</v>
+        <v>500 g</v>
       </c>
       <c r="G14">
         <v>4.9</v>
       </c>
       <c r="H14">
-        <v>420</v>
+        <v>306</v>
       </c>
       <c r="I14" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/013_Tata_Tea.jpg</v>
       </c>
       <c r="J14" t="str">
-        <v>Sun-dried farm toor dal without synthetic water or oil polish, yielding thick aromatic sambar with natural sweetness.</v>
+        <v>Tata Tea Premium blend of gentle rolled tea leaves and long leaves.</v>
       </c>
       <c r="K14" t="str">
-        <v>Origin: Latur, Maharashtra. 100% unpolished. Cooks easily with rich creamy froth and hearty aroma.</v>
+        <v>Rich aromatic cup that brings warmth to your morning routine.</v>
       </c>
       <c r="L14" t="str">
         <v>In Stock</v>
@@ -936,34 +936,34 @@
         <v>GS-1014</v>
       </c>
       <c r="B15" t="str">
-        <v>Farm Fresh Green Moong Whole</v>
+        <v>Brooke Bond Red Label</v>
       </c>
       <c r="C15" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Tea &amp; Coffee</v>
       </c>
       <c r="D15">
-        <v>135</v>
+        <v>310</v>
       </c>
       <c r="E15">
-        <v>160</v>
+        <v>360</v>
       </c>
       <c r="F15" t="str">
-        <v>1 kg</v>
+        <v>500 g</v>
       </c>
       <c r="G15">
         <v>4.8</v>
       </c>
       <c r="H15">
-        <v>195</v>
+        <v>323</v>
       </c>
       <c r="I15" t="str">
-        <v>https://images.unsplash.com/photo-1546069901-ba9599a7e63c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/014_Brooke_Bond_Red_Label.jpg</v>
       </c>
       <c r="J15" t="str">
-        <v>Plump green whole gram with 98%+ germination rate for super-sprouts, dal fry, and traditional cheela.</v>
+        <v>Famous Red Label tea with natural care and delightful flavour.</v>
       </c>
       <c r="K15" t="str">
-        <v>High plant protein (24g/100g). Sun-cured on open farm yards without chemical fumigation.</v>
+        <v>Selected Assam and Dooars teas blended for briskness and strength.</v>
       </c>
       <c r="L15" t="str">
         <v>In Stock</v>
@@ -974,34 +974,34 @@
         <v>GS-1015</v>
       </c>
       <c r="B16" t="str">
-        <v>Yellow Split Moong Dal (Dhuli)</v>
+        <v>AVT Tea</v>
       </c>
       <c r="C16" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Tea &amp; Coffee</v>
       </c>
       <c r="D16">
-        <v>145</v>
+        <v>260</v>
       </c>
       <c r="E16">
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="F16" t="str">
-        <v>1 kg</v>
+        <v>500 g</v>
       </c>
       <c r="G16">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H16">
-        <v>260</v>
+        <v>340</v>
       </c>
       <c r="I16" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/015_AVT_Tea.jpg</v>
       </c>
       <c r="J16" t="str">
-        <v>Ultra-clean, light split moong dal that boils down into comforting soothing kitchari and festive sweet halwa.</v>
+        <v>AVT Premium dust tea, the traditional favourite in Southern households.</v>
       </c>
       <c r="K16" t="str">
-        <v>Easy to digest, recommended for detox diets and post-recovery nourishing broths.</v>
+        <v>Extra strong decoction and full-bodied classic taste.</v>
       </c>
       <c r="L16" t="str">
         <v>In Stock</v>
@@ -1012,34 +1012,34 @@
         <v>GS-1016</v>
       </c>
       <c r="B17" t="str">
-        <v>Whole Black Urad Dal with Husk</v>
+        <v>Coffee Powder</v>
       </c>
       <c r="C17" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Tea &amp; Coffee</v>
       </c>
       <c r="D17">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="E17">
-        <v>210</v>
+        <v>165</v>
       </c>
       <c r="F17" t="str">
-        <v>1 kg</v>
+        <v>200 g</v>
       </c>
       <c r="G17">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H17">
-        <v>310</v>
+        <v>357</v>
       </c>
       <c r="I17" t="str">
-        <v>https://images.unsplash.com/photo-1512621776951-a57141f2eefd?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/016_Coffee_Powder.jpg</v>
       </c>
       <c r="J17" t="str">
-        <v>Heritage jet-black whole lentils essential for velvety Punjabi Dal Makhani and traditional bone-strengthening porridge.</v>
+        <v>Traditional South Indian degree filter coffee blend with roasted chicory.</v>
       </c>
       <c r="K17" t="str">
-        <v>Origin: Guntur soil. Dense in iron, calcium, and plant mucilage for digestive health.</v>
+        <v>80% Arabica/Robusta plantation beans and 20% French chicory.</v>
       </c>
       <c r="L17" t="str">
         <v>In Stock</v>
@@ -1050,34 +1050,34 @@
         <v>GS-1017</v>
       </c>
       <c r="B18" t="str">
-        <v>Gota White Urad Dal (Idli Special)</v>
+        <v>Bru Instant Coffee</v>
       </c>
       <c r="C18" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Tea &amp; Coffee</v>
       </c>
       <c r="D18">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="E18">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="F18" t="str">
-        <v>1 kg</v>
+        <v>100 g</v>
       </c>
       <c r="G18">
         <v>4.9</v>
       </c>
       <c r="H18">
-        <v>480</v>
+        <v>374</v>
       </c>
       <c r="I18" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/017_Bru_Instant_Coffee.jpg</v>
       </c>
       <c r="J18" t="str">
-        <v>Whole round de-husked urad dal with outstanding fermenting capacity that yields cloud-soft, spongy idlis and crisp vadas.</v>
+        <v>Authentic instant coffee made from a fine blend of coffee and chicory.</v>
       </c>
       <c r="K18" t="str">
-        <v>Superior batter volume expansion of 2.4x. Completely free from talc or synthetic brightening agents.</v>
+        <v>Delivers a rich aroma and authentic coffee experience in seconds.</v>
       </c>
       <c r="L18" t="str">
         <v>In Stock</v>
@@ -1088,34 +1088,34 @@
         <v>GS-1018</v>
       </c>
       <c r="B19" t="str">
-        <v>Kashmiri Red Kidney Beans (Rajma Chitra)</v>
+        <v>Nescafe</v>
       </c>
       <c r="C19" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Tea &amp; Coffee</v>
       </c>
       <c r="D19">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="E19">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="F19" t="str">
-        <v>1 kg</v>
+        <v>100 g</v>
       </c>
       <c r="G19">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H19">
-        <v>275</v>
+        <v>391</v>
       </c>
       <c r="I19" t="str">
-        <v>https://images.unsplash.com/photo-1551462147-ff29053fad38?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/018_Nescafe.jpg</v>
       </c>
       <c r="J19" t="str">
-        <v>Speckled high-altitude kidney beans that melt tender when cooked, infusing gravies with deep buttery richness.</v>
+        <v>Nescafe Classic pure instant soluble coffee granules with signature taste.</v>
       </c>
       <c r="K19" t="str">
-        <v>Origin: Bhaderwah, Jammu &amp; Kashmir. High natural mineral content and soft, silky skin.</v>
+        <v>100% pure roasted coffee beans from world-class estates.</v>
       </c>
       <c r="L19" t="str">
         <v>In Stock</v>
@@ -1126,16 +1126,16 @@
         <v>GS-1019</v>
       </c>
       <c r="B20" t="str">
-        <v>Jumbo Kabuli Chickpeas (Garbanzo Beans)</v>
+        <v>Chakra Gold Sugar</v>
       </c>
       <c r="C20" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Sugar &amp; Sweeteners</v>
       </c>
       <c r="D20">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="E20">
-        <v>205</v>
+        <v>60</v>
       </c>
       <c r="F20" t="str">
         <v>1 kg</v>
@@ -1144,16 +1144,16 @@
         <v>4.8</v>
       </c>
       <c r="H20">
-        <v>230</v>
+        <v>408</v>
       </c>
       <c r="I20" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/019_Chakra_Gold_Sugar.jpg</v>
       </c>
       <c r="J20" t="str">
-        <v>Even-sized 12mm jumbo chickpeas perfect for Amritsari Pindi Chole, fresh creamy hummus, and Mediterranean salads.</v>
+        <v>Crystal pure sulphur-free refined white sugar with sparkling clarity.</v>
       </c>
       <c r="K20" t="str">
-        <v>Grade A handpicked. Firm outer bite with tender buttery core upon pressure cooking.</v>
+        <v>100% cane sugar, hygienic untouched packaging.</v>
       </c>
       <c r="L20" t="str">
         <v>In Stock</v>
@@ -1164,34 +1164,34 @@
         <v>GS-1020</v>
       </c>
       <c r="B21" t="str">
-        <v>Desi Brown Chana (Kala Chana)</v>
+        <v>Sugar</v>
       </c>
       <c r="C21" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Sugar &amp; Sweeteners</v>
       </c>
       <c r="D21">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="E21">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="F21" t="str">
         <v>1 kg</v>
       </c>
       <c r="G21">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H21">
-        <v>180</v>
+        <v>425</v>
       </c>
       <c r="I21" t="str">
-        <v>https://images.unsplash.com/photo-1546069901-ba9599a7e63c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/020_Sugar.jpg</v>
       </c>
       <c r="J21" t="str">
-        <v>Nutty indigenous small brown chickpeas, powerhouse of dietary iron and sustained muscle fuel.</v>
+        <v>Clean granulated white cane sugar for daily sweets, tea, and cooking.</v>
       </c>
       <c r="K21" t="str">
-        <v>Traditional rainfed variety. Excellent for sundal, morning sprout salads, and spicy curries.</v>
+        <v>Pure refined sugar with sparkling white grains.</v>
       </c>
       <c r="L21" t="str">
         <v>In Stock</v>
@@ -1202,34 +1202,34 @@
         <v>GS-1021</v>
       </c>
       <c r="B22" t="str">
-        <v>Red Masoor Dal (Split Red Lentils)</v>
+        <v>Jaggery</v>
       </c>
       <c r="C22" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Sugar &amp; Sweeteners</v>
       </c>
       <c r="D22">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="E22">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="F22" t="str">
         <v>1 kg</v>
       </c>
       <c r="G22">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H22">
-        <v>145</v>
+        <v>442</v>
       </c>
       <c r="I22" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/021_Jaggery.jpg</v>
       </c>
       <c r="J22" t="str">
-        <v>Quick-cooking vibrant salmon-pink lentils that melt in 15 minutes into a rich, golden, velvety stew.</v>
+        <v>Traditional unrefined country cane jaggery (Vellam) loaded with natural iron.</v>
       </c>
       <c r="K22" t="str">
-        <v>Cooks fast with no prior soaking required. High in folate, potassium, and plant protein.</v>
+        <v>Free from artificial chemicals, ideal for pongal and traditional sweets.</v>
       </c>
       <c r="L22" t="str">
         <v>In Stock</v>
@@ -1240,34 +1240,34 @@
         <v>GS-1022</v>
       </c>
       <c r="B23" t="str">
-        <v>Horse Gram (Kollu / Kulthi)</v>
+        <v>Rock Sugar / Kalkandu</v>
       </c>
       <c r="C23" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Sugar &amp; Sweeteners</v>
       </c>
       <c r="D23">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E23">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="F23" t="str">
         <v>500 g</v>
       </c>
       <c r="G23">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H23">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="I23" t="str">
-        <v>https://images.unsplash.com/photo-1512621776951-a57141f2eefd?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/022_Rock_Sugar___Kalkandu.jpg</v>
       </c>
       <c r="J23" t="str">
-        <v>Ancient thermogenic super-pulse renowned in Ayurveda for metabolic vitality, weight balance, and kidney health.</v>
+        <v>Pure crystallized diamond sugar rocks, soothing for throat and refreshing.</v>
       </c>
       <c r="K23" t="str">
-        <v>Rich in calcium and polyphenols. Popular for traditional rasam, soups, and dry roasted podis.</v>
+        <v>Traditional Kalkandu for sweet pongal, milk, and ayurvedic remedies.</v>
       </c>
       <c r="L23" t="str">
         <v>In Stock</v>
@@ -1278,34 +1278,34 @@
         <v>GS-1023</v>
       </c>
       <c r="B24" t="str">
-        <v>Roasted Gram / Chutney Dal (Pottukadalai)</v>
+        <v>Gold Winner Sunflower Oil</v>
       </c>
       <c r="C24" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Cooking Oil</v>
       </c>
       <c r="D24">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="E24">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="F24" t="str">
-        <v>1 kg</v>
+        <v>1 L</v>
       </c>
       <c r="G24">
         <v>4.9</v>
       </c>
       <c r="H24">
-        <v>310</v>
+        <v>116</v>
       </c>
       <c r="I24" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/023_Gold_Winner_Sunflower_Oil.jpg</v>
       </c>
       <c r="J24" t="str">
-        <v>Crispy wood-roasted split chickpeas that add body to coconut chutneys, snack mixtures, and festive laddoos.</v>
+        <v>Refined sunflower oil enriched with Vitamin A &amp; D, light on stomach.</v>
       </c>
       <c r="K24" t="str">
-        <v>Ready to eat snack or culinary staple. Crispy golden crunch with zero added oil.</v>
+        <v>Non-greasy, high smoke point for crispy golden frying.</v>
       </c>
       <c r="L24" t="str">
         <v>In Stock</v>
@@ -1316,34 +1316,34 @@
         <v>GS-1024</v>
       </c>
       <c r="B25" t="str">
-        <v>Pure Vedic A2 Desi Gir Cow Cultured Bilona Ghee</v>
+        <v>Sunflower Oil (other brands)</v>
       </c>
       <c r="C25" t="str">
-        <v>Cold-Pressed Oils &amp; Pure Ghee</v>
+        <v>Cooking Oil</v>
       </c>
       <c r="D25">
-        <v>1450</v>
+        <v>138</v>
       </c>
       <c r="E25">
-        <v>1750</v>
+        <v>155</v>
       </c>
       <c r="F25" t="str">
-        <v>500 ml</v>
+        <v>1 L</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H25">
-        <v>615</v>
+        <v>133</v>
       </c>
       <c r="I25" t="str">
-        <v>https://images.unsplash.com/photo-1628088062854-d1870b4553da?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/024_Sunflower_Oil_(other_brands).jpg</v>
       </c>
       <c r="J25" t="str">
-        <v>Crafted through the ancient 5-step Bilona method from curd of grass-fed native Gir cows. Granular danedar golden texture with divine aroma.</v>
+        <v>Pure refined sunflower cooking oil for wholesome, heart-healthy family cooking.</v>
       </c>
       <c r="K25" t="str">
-        <v>Cultured curd churned with wooden bilona, slow-simmered on low flame. Packed in UV-protective amber glass jar.</v>
+        <v>Zero cholesterol, enriched with natural Vitamin E.</v>
       </c>
       <c r="L25" t="str">
         <v>In Stock</v>
@@ -1354,34 +1354,34 @@
         <v>GS-1025</v>
       </c>
       <c r="B26" t="str">
-        <v>Wood-Pressed Virgin Groundnut Oil (Marachekku)</v>
+        <v>Groundnut Oil</v>
       </c>
       <c r="C26" t="str">
-        <v>Cold-Pressed Oils &amp; Pure Ghee</v>
+        <v>Cooking Oil</v>
       </c>
       <c r="D26">
-        <v>340</v>
+        <v>195</v>
       </c>
       <c r="E26">
-        <v>395</v>
+        <v>230</v>
       </c>
       <c r="F26" t="str">
-        <v>1 Litre</v>
+        <v>1 L</v>
       </c>
       <c r="G26">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H26">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="I26" t="str">
-        <v>https://images.unsplash.com/photo-1474979266404-7eaacbcd87c5?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/025_Groundnut_Oil.jpg</v>
       </c>
       <c r="J26" t="str">
-        <v>Extracted in slow wooden expellers (Vagai wood) from sun-dried native groundnuts with zero heat and zero chemicals.</v>
+        <v>Traditional cold-pressed groundnut oil (Kadalai Ennai) with nutty aroma.</v>
       </c>
       <c r="K26" t="str">
-        <v>Unrefined, unbleached, sedimentation filtered. High smoke point with sweet nutty aroma for wholesome daily frying.</v>
+        <v>Wood-pressed / filtered from premium farm groundnuts.</v>
       </c>
       <c r="L26" t="str">
         <v>In Stock</v>
@@ -1392,34 +1392,34 @@
         <v>GS-1026</v>
       </c>
       <c r="B27" t="str">
-        <v>Wood-Pressed Gingelly / Sesame Oil with Palm Jaggery</v>
+        <v>Gingelly / Sesame Oil</v>
       </c>
       <c r="C27" t="str">
-        <v>Cold-Pressed Oils &amp; Pure Ghee</v>
+        <v>Cooking Oil</v>
       </c>
       <c r="D27">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="E27">
-        <v>490</v>
+        <v>280</v>
       </c>
       <c r="F27" t="str">
-        <v>1 Litre</v>
+        <v>1 L</v>
       </c>
       <c r="G27">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H27">
-        <v>380</v>
+        <v>167</v>
       </c>
       <c r="I27" t="str">
-        <v>https://images.unsplash.com/photo-1474979266404-7eaacbcd87c5?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/026_Gingelly___Sesame_Oil.jpg</v>
       </c>
       <c r="J27" t="str">
-        <v>Traditional cold extraction of black sesame seeds blended with authentic palm jaggery to pacify sharpness and maximize antioxidants.</v>
+        <v>Authentic cold-pressed sesame oil (Nallennai) sweetened with palm jaggery.</v>
       </c>
       <c r="K27" t="str">
-        <v>Sourced from Erode oil mills. Ideal for traditional South Indian culinary temperings and oil-pulling.</v>
+        <v>Essential staple for Tamil kuzhambu, idli podi, and oil baths.</v>
       </c>
       <c r="L27" t="str">
         <v>In Stock</v>
@@ -1430,34 +1430,34 @@
         <v>GS-1027</v>
       </c>
       <c r="B28" t="str">
-        <v>Extra Virgin Cold-Pressed Coconut Oil (Raw)</v>
+        <v>Coconut Oil</v>
       </c>
       <c r="C28" t="str">
-        <v>Cold-Pressed Oils &amp; Pure Ghee</v>
+        <v>Cooking Oil</v>
       </c>
       <c r="D28">
-        <v>360</v>
+        <v>210</v>
       </c>
       <c r="E28">
-        <v>425</v>
+        <v>250</v>
       </c>
       <c r="F28" t="str">
-        <v>1 Litre</v>
+        <v>1 L</v>
       </c>
       <c r="G28">
         <v>4.9</v>
       </c>
       <c r="H28">
-        <v>395</v>
+        <v>184</v>
       </c>
       <c r="I28" t="str">
-        <v>https://images.unsplash.com/photo-1526947425960-945c6e72858f?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/027_Coconut_Oil.jpg</v>
       </c>
       <c r="J28" t="str">
-        <v>Made from fresh mature coastal coconuts within hours of harvesting. Crystal clear with delicate tropical aroma.</v>
+        <v>Pure filtered coconut oil extracted from fresh sun-dried copra.</v>
       </c>
       <c r="K28" t="str">
-        <v>Rich in Medium Chain Triglycerides (MCTs) &amp; Lauric Acid. 100% raw edible, hair, and skincare grade.</v>
+        <v>Dual use for traditional cooking and hair nourishment.</v>
       </c>
       <c r="L28" t="str">
         <v>In Stock</v>
@@ -1468,34 +1468,34 @@
         <v>GS-1028</v>
       </c>
       <c r="B29" t="str">
-        <v>Kachi Ghani Raw Mustard Oil (Sarson)</v>
+        <v>Palmolein Oil</v>
       </c>
       <c r="C29" t="str">
-        <v>Cold-Pressed Oils &amp; Pure Ghee</v>
+        <v>Cooking Oil</v>
       </c>
       <c r="D29">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="E29">
-        <v>285</v>
+        <v>125</v>
       </c>
       <c r="F29" t="str">
-        <v>1 Litre</v>
+        <v>1 L</v>
       </c>
       <c r="G29">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H29">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="I29" t="str">
-        <v>https://images.unsplash.com/photo-1474979266404-7eaacbcd87c5?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/028_Palmolein_Oil.jpg</v>
       </c>
       <c r="J29" t="str">
-        <v>Pungent, authentic cold-pressed mustard oil with natural allylisothiocyanate bite that elevates Bengali and North Indian cooking.</v>
+        <v>Refined palmolein cooking oil, economical and heat-stable for daily frying.</v>
       </c>
       <c r="K29" t="str">
-        <v>Cold-pressed from small black mustard seeds in Rajasthan. Preserves natural antioxidants and Omega-3 fatty acids.</v>
+        <v>Ideal for deep frying snacks, murukku, and street foods.</v>
       </c>
       <c r="L29" t="str">
         <v>In Stock</v>
@@ -1506,34 +1506,34 @@
         <v>GS-1029</v>
       </c>
       <c r="B30" t="str">
-        <v>Cold-Pressed Niger Seed Oil (Uchellu)</v>
+        <v>Rice Bran Oil</v>
       </c>
       <c r="C30" t="str">
-        <v>Cold-Pressed Oils &amp; Pure Ghee</v>
+        <v>Cooking Oil</v>
       </c>
       <c r="D30">
-        <v>390</v>
+        <v>135</v>
       </c>
       <c r="E30">
-        <v>460</v>
+        <v>155</v>
       </c>
       <c r="F30" t="str">
-        <v>1 Litre</v>
+        <v>1 L</v>
       </c>
       <c r="G30">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H30">
-        <v>65</v>
+        <v>218</v>
       </c>
       <c r="I30" t="str">
-        <v>https://images.unsplash.com/photo-1474979266404-7eaacbcd87c5?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/029_Rice_Bran_Oil.jpg</v>
       </c>
       <c r="J30" t="str">
-        <v>Tribal cold-pressed edible oil celebrated for intense nutty flavor, linoleic acid, and cardiac health support.</v>
+        <v>Physically refined rice bran oil rich in natural Oryzanol for heart health.</v>
       </c>
       <c r="K30" t="str">
-        <v>Extracted from wild rainfed niger seeds harvested in Eastern Ghats.</v>
+        <v>High smoke point (250°C), absorbs less oil in fried snacks.</v>
       </c>
       <c r="L30" t="str">
         <v>In Stock</v>
@@ -1544,34 +1544,34 @@
         <v>GS-1030</v>
       </c>
       <c r="B31" t="str">
-        <v>Pure Buffalo Milk Desi Ghee (Rich Aromatic)</v>
+        <v>Deepam / Pooja Oil</v>
       </c>
       <c r="C31" t="str">
-        <v>Cold-Pressed Oils &amp; Pure Ghee</v>
+        <v>Cooking Oil</v>
       </c>
       <c r="D31">
-        <v>650</v>
+        <v>120</v>
       </c>
       <c r="E31">
-        <v>750</v>
+        <v>140</v>
       </c>
       <c r="F31" t="str">
-        <v>1 Litre</v>
+        <v>1 L</v>
       </c>
       <c r="G31">
         <v>4.8</v>
       </c>
       <c r="H31">
-        <v>190</v>
+        <v>235</v>
       </c>
       <c r="I31" t="str">
-        <v>https://images.unsplash.com/photo-1628088062854-d1870b4553da?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/030_Deepam___Pooja_Oil.jpg</v>
       </c>
       <c r="J31" t="str">
-        <v>Silky, ivory-white, high-fat ghee from pasture-grazed Murrah buffaloes. Gives unmatched crispness to parathas and sweets.</v>
+        <v>Sacred 5-oil Pancha Deepam oil blend with divine lingering fragrance.</v>
       </c>
       <c r="K31" t="str">
-        <v>Origin: Haryana plains. Clarified butter with luscious creamy taste and higher smoke point.</v>
+        <v>Blended with sesame, mahua, neem, castor, and pure cow ghee.</v>
       </c>
       <c r="L31" t="str">
         <v>In Stock</v>
@@ -1582,34 +1582,34 @@
         <v>GS-1031</v>
       </c>
       <c r="B32" t="str">
-        <v>Alleppey Extra Bold Green Cardamom (8mm+)</v>
+        <v>Vim Dishwash Bar</v>
       </c>
       <c r="C32" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Dishwash</v>
       </c>
       <c r="D32">
-        <v>490</v>
+        <v>20</v>
       </c>
       <c r="E32">
-        <v>580</v>
+        <v>25</v>
       </c>
       <c r="F32" t="str">
-        <v>100 g</v>
+        <v>200 g</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H32">
-        <v>320</v>
+        <v>252</v>
       </c>
       <c r="I32" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/031_Vim_Dishwash_Bar.jpg</v>
       </c>
       <c r="J32" t="str">
-        <v>The Queen of Spices: massive emerald green pods packed with essential-oil-dense seeds bursting with eucalyptus citrus sweetness.</v>
+        <v>Vim bar with the power of 100 lemons that slices through stubborn burnt grease.</v>
       </c>
       <c r="K32" t="str">
-        <v>Grade: 8mm Jumbo Bold. Harvested in the Cardamom Hills of Idukki, Kerala. Sun-dried in traditional kiln dryers.</v>
+        <v>Formulated with real lemon extract and anti-germ mineral particles.</v>
       </c>
       <c r="L32" t="str">
         <v>In Stock</v>
@@ -1620,34 +1620,34 @@
         <v>GS-1032</v>
       </c>
       <c r="B33" t="str">
-        <v>Salem Pure Golden Curcumin Turmeric Powder</v>
+        <v>Vim Dishwash Liquid</v>
       </c>
       <c r="C33" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Dishwash</v>
       </c>
       <c r="D33">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E33">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F33" t="str">
-        <v>250 g</v>
+        <v>500 ml</v>
       </c>
       <c r="G33">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H33">
-        <v>410</v>
+        <v>269</v>
       </c>
       <c r="I33" t="str">
-        <v>https://images.unsplash.com/photo-1615485500704-8e990f9900f7?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/032_Vim_Dishwash_Liquid.jpg</v>
       </c>
       <c r="J33" t="str">
-        <v>Stone-pulverized from whole Salem finger turmeric with certified 4.5%+ active curcumin. Pure golden warmth without starch fillers.</v>
+        <v>Concentrated lemon dishwash gel, leaves vessels sparkling clean without residue.</v>
       </c>
       <c r="K33" t="str">
-        <v>Zero lead chromate, zero artificial dyes. Tested pure for daily golden milk (haldi doodh) and healing cuisine.</v>
+        <v>1 spoon is enough for an entire sink full of utensils.</v>
       </c>
       <c r="L33" t="str">
         <v>In Stock</v>
@@ -1658,34 +1658,34 @@
         <v>GS-1033</v>
       </c>
       <c r="B34" t="str">
-        <v>Tellicherry Whole Black Peppercorns (TGSEB)</v>
+        <v>Exo Dishwash Bar</v>
       </c>
       <c r="C34" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Dishwash</v>
       </c>
       <c r="D34">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="E34">
-        <v>260</v>
+        <v>32</v>
       </c>
       <c r="F34" t="str">
-        <v>200 g</v>
+        <v>250 g</v>
       </c>
       <c r="G34">
         <v>4.9</v>
       </c>
       <c r="H34">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="I34" t="str">
-        <v>https://images.unsplash.com/photo-1509358271058-acd22cc93898?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/033_Exo_Dishwash_Bar.jpg</v>
       </c>
       <c r="J34" t="str">
-        <v>Tellicherry Garbled Special Extra Bold: vine-ripened berries dried naturally to yield deep complex citrus and woodsy heat.</v>
+        <v>Anti-bacterial round dishwash bar with ginger and lime power that prevents sogginess.</v>
       </c>
       <c r="K34" t="str">
-        <v>Hand-graded for size (&gt;4.75mm). Origin: Thalassery coast, Malabar. The world gold-standard of pepper.</v>
+        <v>Touch and shine technology that kills 99.9% utensil bacteria.</v>
       </c>
       <c r="L34" t="str">
         <v>In Stock</v>
@@ -1696,34 +1696,34 @@
         <v>GS-1034</v>
       </c>
       <c r="B35" t="str">
-        <v>Authentic Kashmiri Mongra Saffron (Grade A1)</v>
+        <v>Pril Dishwash Liquid</v>
       </c>
       <c r="C35" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Dishwash</v>
       </c>
       <c r="D35">
-        <v>480</v>
+        <v>105</v>
       </c>
       <c r="E35">
-        <v>590</v>
+        <v>125</v>
       </c>
       <c r="F35" t="str">
-        <v>1 g</v>
+        <v>425 ml</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H35">
-        <v>195</v>
+        <v>303</v>
       </c>
       <c r="I35" t="str">
-        <v>https://images.unsplash.com/photo-1608686207856-001b95cf60ca?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/034_Pril_Dishwash_Liquid.jpg</v>
       </c>
       <c r="J35" t="str">
-        <v>100% pure thick red stigmas harvested from purple saffron crocus fields of Pampore, Kashmir. Divine royal aroma and color.</v>
+        <v>Kraft gel with German degreasing formula that cleans burnt food effortlessly.</v>
       </c>
       <c r="K35" t="str">
-        <v>GI Tagged origin Pampore. Highest crocin and safranal content. Preserved in airtight protective glass vial.</v>
+        <v>Active power droplets cut through oily grease with minimal scrub.</v>
       </c>
       <c r="L35" t="str">
         <v>In Stock</v>
@@ -1734,34 +1734,34 @@
         <v>GS-1035</v>
       </c>
       <c r="B36" t="str">
-        <v>Ceylon True Cinnamon Quills (Alba Grade)</v>
+        <v>Scrub Pad</v>
       </c>
       <c r="C36" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Dishwash</v>
       </c>
       <c r="D36">
-        <v>280</v>
+        <v>35</v>
       </c>
       <c r="E36">
-        <v>340</v>
+        <v>45</v>
       </c>
       <c r="F36" t="str">
-        <v>100 g</v>
+        <v>Pack of 3</v>
       </c>
       <c r="G36">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H36">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="I36" t="str">
-        <v>https://images.unsplash.com/photo-1509358271058-acd22cc93898?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/035_Scrub_Pad.jpg</v>
       </c>
       <c r="J36" t="str">
-        <v>Paper-thin, multi-layered sweet cinnamon scrolls with negligible coumarin content, safe for regular dietary wellness.</v>
+        <v>Heavy-duty nylon green scrub pad for spotless stainless steel and non-stick cookware.</v>
       </c>
       <c r="K36" t="str">
-        <v>Authentic Cinnamomum verum (Ceylon). Subtle fragrant sweet woody flavor, distinct from cheap cassia bark.</v>
+        <v>Durable, non-scratching synthetic scrubbing fibers.</v>
       </c>
       <c r="L36" t="str">
         <v>In Stock</v>
@@ -1772,16 +1772,16 @@
         <v>GS-1036</v>
       </c>
       <c r="B37" t="str">
-        <v>Guntur Stemless Dry Red Chilli (Teja Variety)</v>
+        <v>Rin Detergent Bar</v>
       </c>
       <c r="C37" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Laundry Detergent</v>
       </c>
       <c r="D37">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="E37">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="F37" t="str">
         <v>250 g</v>
@@ -1790,16 +1790,16 @@
         <v>4.8</v>
       </c>
       <c r="H37">
-        <v>220</v>
+        <v>337</v>
       </c>
       <c r="I37" t="str">
-        <v>https://images.unsplash.com/photo-1588252303782-cb80119abd6d?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/036_Rin_Detergent_Bar.jpg</v>
       </c>
       <c r="J37" t="str">
-        <v>Fiery, sun-dried red chillies with clean de-stemmed pods, delivering deep scarlet natural color and electrifying heat.</v>
+        <v>Rin advanced bar for dazzling, mirror-bright whiteness on school uniforms and shirts.</v>
       </c>
       <c r="K37" t="str">
-        <v>Scoville Heat Units: 65,000+. De-stemmed by hand to guarantee pure spice weight without trash stem waste.</v>
+        <v>Bright cleaning technology targets tough cuffs and collar stains.</v>
       </c>
       <c r="L37" t="str">
         <v>In Stock</v>
@@ -1810,34 +1810,34 @@
         <v>GS-1037</v>
       </c>
       <c r="B38" t="str">
-        <v>Organic Whole Cumin Seeds (Jeera)</v>
+        <v>Rin Washing Powder</v>
       </c>
       <c r="C38" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Laundry Detergent</v>
       </c>
       <c r="D38">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="E38">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="F38" t="str">
-        <v>250 g</v>
+        <v>1 kg</v>
       </c>
       <c r="G38">
         <v>4.9</v>
       </c>
       <c r="H38">
-        <v>310</v>
+        <v>354</v>
       </c>
       <c r="I38" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/037_Rin_Washing_Powder.jpg</v>
       </c>
       <c r="J38" t="str">
-        <v>Intensely fragrant small seed cumin with high volatile thymol oil, crackles with earthy warmth in hot ghee.</v>
+        <v>Rin golden shine detergent powder with water-softening enzymes.</v>
       </c>
       <c r="K38" t="str">
-        <v>Origin: Unjha, Gujarat. Machine cleaned and de-stoned, 99.8% pure seed count.</v>
+        <v>Delivers crisp spotless whites in bucket wash and semi-automatic machines.</v>
       </c>
       <c r="L38" t="str">
         <v>In Stock</v>
@@ -1848,34 +1848,34 @@
         <v>GS-1038</v>
       </c>
       <c r="B39" t="str">
-        <v>Small Black Mustard Seeds (Rai / Kadugu)</v>
+        <v>Ariel Washing Powder</v>
       </c>
       <c r="C39" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Laundry Detergent</v>
       </c>
       <c r="D39">
-        <v>45</v>
+        <v>165</v>
       </c>
       <c r="E39">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="F39" t="str">
-        <v>200 g</v>
+        <v>1 kg</v>
       </c>
       <c r="G39">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H39">
-        <v>185</v>
+        <v>371</v>
       </c>
       <c r="I39" t="str">
-        <v>https://images.unsplash.com/photo-1509358271058-acd22cc93898?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/038_Ariel_Washing_Powder.jpg</v>
       </c>
       <c r="J39" t="str">
-        <v>Tiny micro-mustard seeds that pop and sing vigorously in hot tadka, imparting irresistible nutty aroma to curries.</v>
+        <v>Ariel Complete with Oxi-Stain removers for tough 1-wash stain removal.</v>
       </c>
       <c r="K39" t="str">
-        <v>Triple sorted and cleaned. Essential daily spice for Indian temperings.</v>
+        <v>Designed for brilliant results in both handwash and top load machines.</v>
       </c>
       <c r="L39" t="str">
         <v>In Stock</v>
@@ -1886,34 +1886,34 @@
         <v>GS-1039</v>
       </c>
       <c r="B40" t="str">
-        <v>Pure Compound Asafoetida Lump (Perungayam / Hing)</v>
+        <v>Ariel Liquid Detergent</v>
       </c>
       <c r="C40" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Laundry Detergent</v>
       </c>
       <c r="D40">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="E40">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="F40" t="str">
-        <v>50 g</v>
+        <v>1 L</v>
       </c>
       <c r="G40">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H40">
-        <v>240</v>
+        <v>388</v>
       </c>
       <c r="I40" t="str">
-        <v>https://images.unsplash.com/photo-1615485500704-8e990f9900f7?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/039_Ariel_Liquid_Detergent.jpg</v>
       </c>
       <c r="J40" t="str">
-        <v>Traditional resin asafoetida with deep umami aroma. A pinhead pinch elevates sambar and digestive rasam instantly.</v>
+        <v>Ariel Matic liquid detergent that dissolves instantly and protects fabric colour.</v>
       </c>
       <c r="K40" t="str">
-        <v>Ferula plant resin. No added wheat fillers or artificial gum binders.</v>
+        <v>Prevents fabric dullness, leaving fresh fragrance and spotless cleaning.</v>
       </c>
       <c r="L40" t="str">
         <v>In Stock</v>
@@ -1924,34 +1924,34 @@
         <v>GS-1040</v>
       </c>
       <c r="B41" t="str">
-        <v>Madurai Stone Ground Coriander Powder (Dhania)</v>
+        <v>Surf Excel Washing Powder</v>
       </c>
       <c r="C41" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Laundry Detergent</v>
       </c>
       <c r="D41">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="E41">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="F41" t="str">
-        <v>250 g</v>
+        <v>1 kg</v>
       </c>
       <c r="G41">
         <v>4.8</v>
       </c>
       <c r="H41">
-        <v>190</v>
+        <v>405</v>
       </c>
       <c r="I41" t="str">
-        <v>https://images.unsplash.com/photo-1615485500704-8e990f9900f7?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/040_Surf_Excel_Washing_Powder.jpg</v>
       </c>
       <c r="J41" t="str">
-        <v>Slow-roasted green coriander seeds ground coarsely to impart refreshing herbal citrus flavor and gravy body.</v>
+        <v>Surf Excel Easy Wash powder with super budget power to remove tough stains.</v>
       </c>
       <c r="K41" t="str">
-        <v>Contains high natural seed essential oils. Zero stale odor.</v>
+        <v>Lathers smoothly in hard water and rinses away without white marks.</v>
       </c>
       <c r="L41" t="str">
         <v>In Stock</v>
@@ -1962,34 +1962,34 @@
         <v>GS-1041</v>
       </c>
       <c r="B42" t="str">
-        <v>Kashmiri Mild Degi Mirch Powder</v>
+        <v>Surf Excel Liquid</v>
       </c>
       <c r="C42" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Laundry Detergent</v>
       </c>
       <c r="D42">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="E42">
-        <v>195</v>
+        <v>270</v>
       </c>
       <c r="F42" t="str">
-        <v>200 g</v>
+        <v>1 L</v>
       </c>
       <c r="G42">
         <v>4.9</v>
       </c>
       <c r="H42">
-        <v>275</v>
+        <v>422</v>
       </c>
       <c r="I42" t="str">
-        <v>https://images.unsplash.com/photo-1588252303782-cb80119abd6d?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/041_Surf_Excel_Liquid.jpg</v>
       </c>
       <c r="J42" t="str">
-        <v>Luminous naturally crimson chilli powder that imparts breathtaking restaurant-style red color with mild, gentle heat.</v>
+        <v>Surf Excel Matic Front &amp; Top Load liquid with active stain fighting molecules.</v>
       </c>
       <c r="K42" t="str">
-        <v>100% pure sun-cured Kashmiri red chillies without Sudan dyes or artificial color enhancers.</v>
+        <v>Gentle on hands and washing machines, keeps clothes like new.</v>
       </c>
       <c r="L42" t="str">
         <v>In Stock</v>
@@ -2000,34 +2000,34 @@
         <v>GS-1042</v>
       </c>
       <c r="B43" t="str">
-        <v>Himalayan Pink Rock Salt (Sendha Namak Fine)</v>
+        <v>Wheel Washing Powder</v>
       </c>
       <c r="C43" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Laundry Detergent</v>
       </c>
       <c r="D43">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E43">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F43" t="str">
         <v>1 kg</v>
       </c>
       <c r="G43">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H43">
-        <v>360</v>
+        <v>439</v>
       </c>
       <c r="I43" t="str">
-        <v>https://images.unsplash.com/photo-1518110925495-5fe2fda0442c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/042_Wheel_Washing_Powder.jpg</v>
       </c>
       <c r="J43" t="str">
-        <v>Unrefined ancient sea salt crystals mined from pristine mountain seams, containing 84 natural trace minerals.</v>
+        <v>Active Wheel 2-in-1 powder with the fresh essence of lemon and jasmine.</v>
       </c>
       <c r="K43" t="str">
-        <v>Pure Sendha Namak suitable for fasting (vrat), balancing electrolytes, and finishing seasoning.</v>
+        <v>Budget-friendly everyday family laundry powder.</v>
       </c>
       <c r="L43" t="str">
         <v>In Stock</v>
@@ -2038,34 +2038,34 @@
         <v>GS-1043</v>
       </c>
       <c r="B44" t="str">
-        <v>Premium California Whole Almonds (Badam Giri)</v>
+        <v>Tide Washing Powder</v>
       </c>
       <c r="C44" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Laundry Detergent</v>
       </c>
       <c r="D44">
-        <v>490</v>
+        <v>125</v>
       </c>
       <c r="E44">
-        <v>620</v>
+        <v>145</v>
       </c>
       <c r="F44" t="str">
-        <v>500 g</v>
+        <v>1 kg</v>
       </c>
       <c r="G44">
         <v>4.9</v>
       </c>
       <c r="H44">
-        <v>410</v>
+        <v>96</v>
       </c>
       <c r="I44" t="str">
-        <v>https://images.unsplash.com/photo-1508061253366-f7da158b6d46?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/043_Tide_Washing_Powder.jpg</v>
       </c>
       <c r="J44" t="str">
-        <v>Crunchy, sweet nonpareil kernels rich in Vitamin E, dietary fiber, and plant-based protein.</v>
+        <v>Tide Plus Extra Power with jasmine and rose fragrance for dazzling whites.</v>
       </c>
       <c r="K44" t="str">
-        <v>100% whole kernels with uniform shape and zero bitter almond contamination.</v>
+        <v>Works fast on yellowing and stubborn turmeric/food stains.</v>
       </c>
       <c r="L44" t="str">
         <v>In Stock</v>
@@ -2076,34 +2076,34 @@
         <v>GS-1044</v>
       </c>
       <c r="B45" t="str">
-        <v>Goan King Whole Cashews (W240 Grade)</v>
+        <v>Ujala / Fabric Whitener</v>
       </c>
       <c r="C45" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Laundry Detergent</v>
       </c>
       <c r="D45">
-        <v>520</v>
+        <v>45</v>
       </c>
       <c r="E45">
-        <v>650</v>
+        <v>52</v>
       </c>
       <c r="F45" t="str">
-        <v>500 g</v>
+        <v>250 ml</v>
       </c>
       <c r="G45">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H45">
-        <v>380</v>
+        <v>113</v>
       </c>
       <c r="I45" t="str">
-        <v>https://images.unsplash.com/photo-1509358271058-acd22cc93898?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/044_Ujala___Fabric_Whitener.jpg</v>
       </c>
       <c r="J45" t="str">
-        <v>Large, buttery white cashew nuts hand-shelled in coastal Konkan plantations. Sweet, crisp, and rich in healthy fats.</v>
+        <v>Ujala Supreme 4-drop fabric whitener for ultra-violet radiant white clothes.</v>
       </c>
       <c r="K45" t="str">
-        <v>Grade: White Whole 240 (King Size). Vacuum sealed for maximum crispness and zero moisture absorption.</v>
+        <v>Contains ultra-white suspension particles for crisp school and office shirts.</v>
       </c>
       <c r="L45" t="str">
         <v>In Stock</v>
@@ -2114,34 +2114,34 @@
         <v>GS-1045</v>
       </c>
       <c r="B46" t="str">
-        <v>Kashmiri Snow-White Walnut Kernels (Akhrot)</v>
+        <v>Comfort Fabric Conditioner</v>
       </c>
       <c r="C46" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Laundry Detergent</v>
       </c>
       <c r="D46">
-        <v>580</v>
+        <v>225</v>
       </c>
       <c r="E46">
-        <v>720</v>
+        <v>260</v>
       </c>
       <c r="F46" t="str">
-        <v>400 g</v>
+        <v>860 ml</v>
       </c>
       <c r="G46">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H46">
-        <v>245</v>
+        <v>130</v>
       </c>
       <c r="I46" t="str">
-        <v>https://images.unsplash.com/photo-1546069901-ba9599a7e63c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/045_Comfort_Fabric_Conditioner.jpg</v>
       </c>
       <c r="J46" t="str">
-        <v>Light amber halved walnut kernels bursting with natural brain-boosting Omega-3 ALA fatty acids and zero bitterness.</v>
+        <v>Comfort after-wash fabric conditioner with 14-day lingering floral fragrance.</v>
       </c>
       <c r="K46" t="str">
-        <v>Origin: Kupwara orchards, Kashmir. Hand-cracked from soft-shell kagzi walnuts.</v>
+        <v>Softens fabric fibres, protects colour and eases ironing.</v>
       </c>
       <c r="L46" t="str">
         <v>In Stock</v>
@@ -2152,34 +2152,34 @@
         <v>GS-1046</v>
       </c>
       <c r="B47" t="str">
-        <v>Royal Medjool Jumbo Dates (Soft &amp; Caramelly)</v>
+        <v>Lifebuoy Soap</v>
       </c>
       <c r="C47" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Bath Soap</v>
       </c>
       <c r="D47">
-        <v>640</v>
+        <v>38</v>
       </c>
       <c r="E47">
-        <v>780</v>
+        <v>42</v>
       </c>
       <c r="F47" t="str">
-        <v>500 g</v>
+        <v>125 g</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H47">
-        <v>290</v>
+        <v>147</v>
       </c>
       <c r="I47" t="str">
-        <v>https://images.unsplash.com/photo-1582281298055-e25b84a30b0b?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/046_Lifebuoy_Soap.jpg</v>
       </c>
       <c r="J47" t="str">
-        <v>The King of Dates: plump, luscious, naturally caramel-sweet fruit with velvety pulp that melts in your mouth.</v>
+        <v>Lifebuoy Total 10 germ protection soap with silver shield technology.</v>
       </c>
       <c r="K47" t="str">
-        <v>100% natural, no glucose dipping, no added sulfur or preservatives. Great natural pre-workout snack.</v>
+        <v>Provides 100% stronger protection against sickness-causing germs.</v>
       </c>
       <c r="L47" t="str">
         <v>In Stock</v>
@@ -2190,34 +2190,34 @@
         <v>GS-1047</v>
       </c>
       <c r="B48" t="str">
-        <v>Afghan Green Long Raisins (Kishmish)</v>
+        <v>Margo Soap</v>
       </c>
       <c r="C48" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Bath Soap</v>
       </c>
       <c r="D48">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="E48">
-        <v>240</v>
+        <v>48</v>
       </c>
       <c r="F48" t="str">
-        <v>250 g</v>
+        <v>125 g</v>
       </c>
       <c r="G48">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H48">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="I48" t="str">
-        <v>https://images.unsplash.com/photo-1508061253366-f7da158b6d46?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/047_Margo_Soap.jpg</v>
       </c>
       <c r="J48" t="str">
-        <v>Slender, sun-dried green raisins with mild tangy sweetness and chewy succulent texture.</v>
+        <v>Original neem bath soap infused with 100% pure neem oil and Vitamin E.</v>
       </c>
       <c r="K48" t="str">
-        <v>Shade dried in mud chambers (kandahar style). Rich in natural iron and potassium.</v>
+        <v>Clears skin blemishes, prevents prickliness, and purifies naturally.</v>
       </c>
       <c r="L48" t="str">
         <v>In Stock</v>
@@ -2228,34 +2228,34 @@
         <v>GS-1048</v>
       </c>
       <c r="B49" t="str">
-        <v>Iranian Salted &amp; Roasted Pistachios (Pista)</v>
+        <v>Lux Soap</v>
       </c>
       <c r="C49" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Bath Soap</v>
       </c>
       <c r="D49">
-        <v>590</v>
+        <v>40</v>
       </c>
       <c r="E49">
-        <v>720</v>
+        <v>46</v>
       </c>
       <c r="F49" t="str">
-        <v>400 g</v>
+        <v>100 g</v>
       </c>
       <c r="G49">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H49">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="I49" t="str">
-        <v>https://images.unsplash.com/photo-1509358271058-acd22cc93898?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/048_Lux_Soap.jpg</v>
       </c>
       <c r="J49" t="str">
-        <v>Naturally smiling pistachios gently dry-roasted in Himalayan pink salt. Emerald green kernels with savory snap.</v>
+        <v>Lux Velvet Touch beauty soap with French rose perfume and almond oil.</v>
       </c>
       <c r="K49" t="str">
-        <v>High lutein, zeaxanthin, and B6. Clean shell opening for effortless snacking.</v>
+        <v>Rich creamy lather leaves skin soft, radiant, and beautifully scented.</v>
       </c>
       <c r="L49" t="str">
         <v>In Stock</v>
@@ -2266,34 +2266,34 @@
         <v>GS-1049</v>
       </c>
       <c r="B50" t="str">
-        <v>Raw Organic Chia Seeds</v>
+        <v>Lifebuoy Handwash</v>
       </c>
       <c r="C50" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Bath Soap</v>
       </c>
       <c r="D50">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="E50">
-        <v>210</v>
+        <v>99</v>
       </c>
       <c r="F50" t="str">
-        <v>250 g</v>
+        <v>185 ml</v>
       </c>
       <c r="G50">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H50">
-        <v>280</v>
+        <v>198</v>
       </c>
       <c r="I50" t="str">
-        <v>https://images.unsplash.com/photo-1518110925495-5fe2fda0442c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/049_Lifebuoy_Handwash.jpg</v>
       </c>
       <c r="J50" t="str">
-        <v>Ancient Aztec superseed that expands 10x in water, loaded with prebiotic fiber and omega-3s.</v>
+        <v>Active silver formula handwash that cleans and kills 99.9% germs in 10 seconds.</v>
       </c>
       <c r="K50" t="str">
-        <v>100% raw unrefined seeds. Ideal for puddings, morning smoothies, and yogurt topping.</v>
+        <v>Moisturizing formula keeps hands clean, safe, and supple.</v>
       </c>
       <c r="L50" t="str">
         <v>In Stock</v>
@@ -2304,34 +2304,34 @@
         <v>GS-1050</v>
       </c>
       <c r="B51" t="str">
-        <v>Roasted Pumpkin Seeds with Himalayan Pink Salt</v>
+        <v>Dettol Soap</v>
       </c>
       <c r="C51" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Bath Soap</v>
       </c>
       <c r="D51">
-        <v>180</v>
+        <v>52</v>
       </c>
       <c r="E51">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="F51" t="str">
-        <v>200 g</v>
+        <v>125 g</v>
       </c>
       <c r="G51">
         <v>4.8</v>
       </c>
       <c r="H51">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="I51" t="str">
-        <v>https://images.unsplash.com/photo-1508061253366-f7da158b6d46?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/050_Dettol_Soap.jpg</v>
       </c>
       <c r="J51" t="str">
-        <v>Crunchy emerald pepitas packed with zinc and magnesium for immune and deep sleep support.</v>
+        <v>Dettol Original bath bar trusted for clinical family germ protection.</v>
       </c>
       <c r="K51" t="str">
-        <v>Slow oven roasted without oil. Delicious keto-friendly snack.</v>
+        <v>Enriched with skin moisturizers and pine antiseptic scent.</v>
       </c>
       <c r="L51" t="str">
         <v>In Stock</v>
@@ -2342,34 +2342,34 @@
         <v>GS-1051</v>
       </c>
       <c r="B52" t="str">
-        <v>Dried Turkish Figs (Anjeer)</v>
+        <v>Santoor Soap</v>
       </c>
       <c r="C52" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Bath Soap</v>
       </c>
       <c r="D52">
-        <v>490</v>
+        <v>38</v>
       </c>
       <c r="E52">
-        <v>610</v>
+        <v>45</v>
       </c>
       <c r="F52" t="str">
-        <v>300 g</v>
+        <v>125 g</v>
       </c>
       <c r="G52">
         <v>4.9</v>
       </c>
       <c r="H52">
-        <v>175</v>
+        <v>232</v>
       </c>
       <c r="I52" t="str">
-        <v>https://images.unsplash.com/photo-1582281298055-e25b84a30b0b?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/051_Santoor_Soap.jpg</v>
       </c>
       <c r="J52" t="str">
-        <v>Tender, honey-sweet whole sun-dried figs packed with tiny crunchy edible seeds and rich dietary iron.</v>
+        <v>Santoor sandalwood and turmeric soap for youthful, glowing, blemish-free skin.</v>
       </c>
       <c r="K52" t="str">
-        <v>Naturally sweet without sugar syrup coating. Soak overnight in milk or water for digestive vitality.</v>
+        <v>Traditional Ayurvedic formulation loved by Indian women for generations.</v>
       </c>
       <c r="L52" t="str">
         <v>In Stock</v>
@@ -2380,34 +2380,34 @@
         <v>GS-1052</v>
       </c>
       <c r="B53" t="str">
-        <v>Raw Wildflower Forest Honey (Unprocessed &amp; Unfiltered)</v>
+        <v>Dove Soap</v>
       </c>
       <c r="C53" t="str">
-        <v>Farm Honey &amp; Country Sugars</v>
+        <v>Bath Soap</v>
       </c>
       <c r="D53">
-        <v>420</v>
+        <v>65</v>
       </c>
       <c r="E53">
-        <v>520</v>
+        <v>75</v>
       </c>
       <c r="F53" t="str">
-        <v>500 g</v>
+        <v>100 g</v>
       </c>
       <c r="G53">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H53">
-        <v>480</v>
+        <v>249</v>
       </c>
       <c r="I53" t="str">
-        <v>https://images.unsplash.com/photo-1587049352846-4a222e784d38?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/052_Dove_Soap.jpg</v>
       </c>
       <c r="J53" t="str">
-        <v>Harvested ethically by indigenous honey hunters from wild hives in deep Nilgiri reserves. Preserves live bee pollen, propolis, and enzymes.</v>
+        <v>Dove Beauty Moisture cream bar with 1/4th moisturizing milk.</v>
       </c>
       <c r="K53" t="str">
-        <v>Zero thermal processing, zero corn syrup or inverted sugar. Pure thick aromatic nectar with multi-floral tasting notes.</v>
+        <v>Gentle cleanser that doesn't dry skin like regular soaps.</v>
       </c>
       <c r="L53" t="str">
         <v>In Stock</v>
@@ -2418,34 +2418,34 @@
         <v>GS-1053</v>
       </c>
       <c r="B54" t="str">
-        <v>Organic Pure Palm Jaggery (Karupatti)</v>
+        <v>Cinthol Soap</v>
       </c>
       <c r="C54" t="str">
-        <v>Farm Honey &amp; Country Sugars</v>
+        <v>Bath Soap</v>
       </c>
       <c r="D54">
-        <v>195</v>
+        <v>45</v>
       </c>
       <c r="E54">
-        <v>240</v>
+        <v>52</v>
       </c>
       <c r="F54" t="str">
-        <v>500 g</v>
+        <v>100 g</v>
       </c>
       <c r="G54">
         <v>4.9</v>
       </c>
       <c r="H54">
-        <v>360</v>
+        <v>266</v>
       </c>
       <c r="I54" t="str">
-        <v>https://images.unsplash.com/photo-1587049352846-4a222e784d38?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/053_Cinthol_Soap.jpg</v>
       </c>
       <c r="J54" t="str">
-        <v>Dark, mineral-dense jaggery boiled from fresh palmyra palm nectar. Has a rich butterscotch finish and high iron content.</v>
+        <v>Cinthol Original soap with deodorizing protection and 99.9% germ shield.</v>
       </c>
       <c r="K54" t="str">
-        <v>Origin: Tirunelveli palm groves. Made with zero bleaching chemicals or sulfur. The ultimate natural sweetener for herbal coffee.</v>
+        <v>Revitalizing freshness keeps you energized all day long.</v>
       </c>
       <c r="L54" t="str">
         <v>In Stock</v>
@@ -2456,34 +2456,34 @@
         <v>GS-1054</v>
       </c>
       <c r="B55" t="str">
-        <v>Country Brown Sugar (Nattu Sakkarai)</v>
+        <v>Medimix Soap</v>
       </c>
       <c r="C55" t="str">
-        <v>Farm Honey &amp; Country Sugars</v>
+        <v>Bath Soap</v>
       </c>
       <c r="D55">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="E55">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="F55" t="str">
-        <v>1 kg</v>
+        <v>125 g</v>
       </c>
       <c r="G55">
         <v>4.8</v>
       </c>
       <c r="H55">
-        <v>430</v>
+        <v>283</v>
       </c>
       <c r="I55" t="str">
-        <v>https://images.unsplash.com/photo-1587049352846-4a222e784d38?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/054_Medimix_Soap.jpg</v>
       </c>
       <c r="J55" t="str">
-        <v>Unrefined cane sugar crystals retaining wholesome molasses minerals. Dissolves smoothly without sour aftertaste.</v>
+        <v>Medimix Ayurvedic 18-herb soap that prevents body odour, acne, and rashes.</v>
       </c>
       <c r="K55" t="str">
-        <v>Made from organically grown cane. Replaces white refined sugar 1:1 in tea, coffee, and traditional baking.</v>
+        <v>Handmade soap enriched with traditional Ayurvedic herbal oils.</v>
       </c>
       <c r="L55" t="str">
         <v>In Stock</v>
@@ -2494,34 +2494,34 @@
         <v>GS-1055</v>
       </c>
       <c r="B56" t="str">
-        <v>Raw Jamun Blossom Monofloral Honey</v>
+        <v>Pears Soap</v>
       </c>
       <c r="C56" t="str">
-        <v>Farm Honey &amp; Country Sugars</v>
+        <v>Bath Soap</v>
       </c>
       <c r="D56">
-        <v>450</v>
+        <v>68</v>
       </c>
       <c r="E56">
-        <v>550</v>
+        <v>78</v>
       </c>
       <c r="F56" t="str">
-        <v>500 g</v>
+        <v>125 g</v>
       </c>
       <c r="G56">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H56">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="I56" t="str">
-        <v>https://images.unsplash.com/photo-1587049352846-4a222e784d38?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/055_Pears_Soap.jpg</v>
       </c>
       <c r="J56" t="str">
-        <v>Rare single-flower honey harvested when black plum (jamun) orchards are in full blossom. Mildly bitter-sweet with glycemic support.</v>
+        <v>Pears Pure &amp; Gentle transparent glycerin soap for clear, soft, radiant skin.</v>
       </c>
       <c r="K56" t="str">
-        <v>Recommended in Ayurveda for blood sugar management. 100% raw and bottled at room temperature.</v>
+        <v>Crafted with 98% pure glycerin and natural cleansing oils.</v>
       </c>
       <c r="L56" t="str">
         <v>In Stock</v>
@@ -2532,34 +2532,34 @@
         <v>GS-1056</v>
       </c>
       <c r="B57" t="str">
-        <v>Organic Sugarcane Jaggery Powder (Gur Shakkar)</v>
+        <v>Arasan Washing Soap</v>
       </c>
       <c r="C57" t="str">
-        <v>Farm Honey &amp; Country Sugars</v>
+        <v>Laundry Soap Bar</v>
       </c>
       <c r="D57">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="E57">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="F57" t="str">
-        <v>1 kg</v>
+        <v>250 g</v>
       </c>
       <c r="G57">
         <v>4.8</v>
       </c>
       <c r="H57">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="I57" t="str">
-        <v>https://images.unsplash.com/photo-1587049352846-4a222e784d38?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/056_Arasan_Washing_Soap.jpg</v>
       </c>
       <c r="J57" t="str">
-        <v>Free-flowing golden jaggery granules crafted from certified organic sugarcane juice using traditional clarifiers.</v>
+        <v>Traditional Tamil Nadu laundry soap bar renowned for tough collar grime removal.</v>
       </c>
       <c r="K57" t="str">
-        <v>Packed with magnesium, iron, and natural trace minerals. Ideal for daily tea and wholesome sweet dishes.</v>
+        <v>Dense, long-lasting bar with strong cleansing lather.</v>
       </c>
       <c r="L57" t="str">
         <v>In Stock</v>
@@ -2570,16 +2570,16 @@
         <v>GS-1057</v>
       </c>
       <c r="B58" t="str">
-        <v>Nilgiri Blue Mountain Orthodox Black Tea (Whole Leaf)</v>
+        <v>Rin Washing Soap</v>
       </c>
       <c r="C58" t="str">
-        <v>Artisanal Teas &amp; Filter Coffee</v>
+        <v>Laundry Soap Bar</v>
       </c>
       <c r="D58">
-        <v>240</v>
+        <v>22</v>
       </c>
       <c r="E58">
-        <v>295</v>
+        <v>25</v>
       </c>
       <c r="F58" t="str">
         <v>250 g</v>
@@ -2588,16 +2588,16 @@
         <v>4.9</v>
       </c>
       <c r="H58">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="I58" t="str">
-        <v>https://images.unsplash.com/photo-1544787219-7f47ccb76574?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/057_Rin_Washing_Soap.jpg</v>
       </c>
       <c r="J58" t="str">
-        <v>Grown at 6,500 ft elevation in the misty Nilgiris. Produces a bright amber cup with floral citrus aroma and crisp brisk finish.</v>
+        <v>Rin bar with brightening agents for crisp whiteness and clean hems.</v>
       </c>
       <c r="K58" t="str">
-        <v>Estate: Coonoor Single Garden. High winter-frost flush. Enjoy pure black or with a splash of milk.</v>
+        <v>Formulated to target grease and soil in manual washing.</v>
       </c>
       <c r="L58" t="str">
         <v>In Stock</v>
@@ -2608,34 +2608,34 @@
         <v>GS-1058</v>
       </c>
       <c r="B59" t="str">
-        <v>Kumbakonam Degree Filter Coffee Blend (80:20)</v>
+        <v>Wheel Washing Soap</v>
       </c>
       <c r="C59" t="str">
-        <v>Artisanal Teas &amp; Filter Coffee</v>
+        <v>Laundry Soap Bar</v>
       </c>
       <c r="D59">
-        <v>260</v>
+        <v>18</v>
       </c>
       <c r="E59">
-        <v>320</v>
+        <v>22</v>
       </c>
       <c r="F59" t="str">
-        <v>500 g</v>
+        <v>250 g</v>
       </c>
       <c r="G59">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H59">
-        <v>530</v>
+        <v>351</v>
       </c>
       <c r="I59" t="str">
-        <v>https://images.unsplash.com/photo-1514432324607-a09d9b4aefdd?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/058_Wheel_Washing_Soap.jpg</v>
       </c>
       <c r="J59" t="str">
-        <v>Signature blend of high-altitude Chikmagalur Arabica and Robusta beans roasted medium-dark, enriched with 20% French chicory.</v>
+        <v>Wheel active lemon and floral washing bar for budget everyday laundry.</v>
       </c>
       <c r="K59" t="str">
-        <v>Gives thick aromatic decoction with rich froth and chocolatey undertone for authentic brass-davarah filter coffee.</v>
+        <v>Quick foaming bar that rinses effortlessly in tap water.</v>
       </c>
       <c r="L59" t="str">
         <v>In Stock</v>
@@ -2646,34 +2646,34 @@
         <v>GS-1059</v>
       </c>
       <c r="B60" t="str">
-        <v>Kashmiri Shahi Kahwa Green Tea with Almonds &amp; Saffron</v>
+        <v>501 Bar Soap</v>
       </c>
       <c r="C60" t="str">
-        <v>Artisanal Teas &amp; Filter Coffee</v>
+        <v>Laundry Soap Bar</v>
       </c>
       <c r="D60">
-        <v>380</v>
+        <v>26</v>
       </c>
       <c r="E60">
-        <v>460</v>
+        <v>30</v>
       </c>
       <c r="F60" t="str">
-        <v>150 g</v>
+        <v>250 g</v>
       </c>
       <c r="G60">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H60">
-        <v>185</v>
+        <v>368</v>
       </c>
       <c r="I60" t="str">
-        <v>https://images.unsplash.com/photo-1544787219-7f47ccb76574?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/059_501_Bar_Soap.jpg</v>
       </c>
       <c r="J60" t="str">
-        <v>Regal blend of fine green tea leaves infused with crushed green cardamom, cinnamon, slivered almonds, and pure Kashmiri saffron threads.</v>
+        <v>Tata 501 legendary heritage washing soap bar for heavy cottons and linens.</v>
       </c>
       <c r="K60" t="str">
-        <v>Warming Himalayan digestive infusion with intoxicating festive aroma. Brews pale golden amber.</v>
+        <v>Time-tested formulation that is tough on stains yet gentle on fabrics.</v>
       </c>
       <c r="L60" t="str">
         <v>In Stock</v>
@@ -2684,34 +2684,34 @@
         <v>GS-1060</v>
       </c>
       <c r="B61" t="str">
-        <v>Organic Moringa &amp; Lemon Tulsi Herbal Infusion</v>
+        <v>Vim Washing Bar</v>
       </c>
       <c r="C61" t="str">
-        <v>Artisanal Teas &amp; Filter Coffee</v>
+        <v>Laundry Soap Bar</v>
       </c>
       <c r="D61">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="E61">
-        <v>225</v>
+        <v>30</v>
       </c>
       <c r="F61" t="str">
-        <v>100 g</v>
+        <v>300 g</v>
       </c>
       <c r="G61">
         <v>4.8</v>
       </c>
       <c r="H61">
-        <v>140</v>
+        <v>385</v>
       </c>
       <c r="I61" t="str">
-        <v>https://images.unsplash.com/photo-1544787219-7f47ccb76574?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/060_Vim_Washing_Bar.jpg</v>
       </c>
       <c r="J61" t="str">
-        <v>Caffeine-free soothing wellness blend of sun-cured drumstick leaves, sacred Krishna Tulsi, and refreshing lemongrass.</v>
+        <v>Multi-utility cleaning bar for vessels, stains, and household surfaces.</v>
       </c>
       <c r="K61" t="str">
-        <v>Immunity boosting and detoxifying herbal tisane. 100% loose leaf organic herbs.</v>
+        <v>Concentrated grease-cutting mineral formula.</v>
       </c>
       <c r="L61" t="str">
         <v>In Stock</v>
@@ -2722,34 +2722,34 @@
         <v>GS-1061</v>
       </c>
       <c r="B62" t="str">
-        <v>Cardamom &amp; Ginger Spiced CTC Chai Mix</v>
+        <v>Sakthi Chilli Powder</v>
       </c>
       <c r="C62" t="str">
-        <v>Artisanal Teas &amp; Filter Coffee</v>
+        <v>Sakthi &amp; Other Cooking Masalas</v>
       </c>
       <c r="D62">
-        <v>210</v>
+        <v>38</v>
       </c>
       <c r="E62">
-        <v>260</v>
+        <v>45</v>
       </c>
       <c r="F62" t="str">
-        <v>500 g</v>
+        <v>100 g</v>
       </c>
       <c r="G62">
         <v>4.9</v>
       </c>
       <c r="H62">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="I62" t="str">
-        <v>https://images.unsplash.com/photo-1514432324607-a09d9b4aefdd?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/061_Sakthi_Chilli_Powder.jpg</v>
       </c>
       <c r="J62" t="str">
-        <v>Robust Assam CTC tea blended with real crushed Malabar dry ginger (sonth) and Idukki green cardamom for morning kick.</v>
+        <v>Sakthi pure hot red chilli powder from selected farm peppers.</v>
       </c>
       <c r="K62" t="str">
-        <v>Strong malty liquor designed to brew perfect Indian kadak chai with milk and jaggery.</v>
+        <v>Bold natural red hue and sizzling spiciness.</v>
       </c>
       <c r="L62" t="str">
         <v>In Stock</v>
@@ -2760,34 +2760,34 @@
         <v>GS-1062</v>
       </c>
       <c r="B63" t="str">
-        <v>Traditional Millet Ribbon Pakoda (Wood-Pressed Groundnut Oil)</v>
+        <v>Sakthi Turmeric Powder</v>
       </c>
       <c r="C63" t="str">
-        <v>Heritage Crisps &amp; Snacks</v>
+        <v>Sakthi &amp; Other Cooking Masalas</v>
       </c>
       <c r="D63">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="E63">
-        <v>145</v>
+        <v>42</v>
       </c>
       <c r="F63" t="str">
-        <v>200 g</v>
+        <v>100 g</v>
       </c>
       <c r="G63">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H63">
-        <v>270</v>
+        <v>419</v>
       </c>
       <c r="I63" t="str">
-        <v>https://images.unsplash.com/photo-1599490659213-e2b9527bd087?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/062_Sakthi_Turmeric_Powder.jpg</v>
       </c>
       <c r="J63" t="str">
-        <v>Golden crispy ribbons made from foxtail millet and roasted gram flour, seasoned with red chilli, hing, and ajwain.</v>
+        <v>Sakthi golden yellow turmeric powder processed hygienically in Erode.</v>
       </c>
       <c r="K63" t="str">
-        <v>Fried exclusively in fresh wood-pressed groundnut oil. Zero palm oil, zero trans-fats, zero food coloring.</v>
+        <v>High curcumin content, completely pure and laboratory tested.</v>
       </c>
       <c r="L63" t="str">
         <v>In Stock</v>
@@ -2798,34 +2798,34 @@
         <v>GS-1063</v>
       </c>
       <c r="B64" t="str">
-        <v>Kerala Nendran Banana Chips in Cold-Pressed Coconut Oil</v>
+        <v>Sakthi Coriander Powder</v>
       </c>
       <c r="C64" t="str">
-        <v>Heritage Crisps &amp; Snacks</v>
+        <v>Sakthi &amp; Other Cooking Masalas</v>
       </c>
       <c r="D64">
-        <v>140</v>
+        <v>36</v>
       </c>
       <c r="E64">
-        <v>170</v>
+        <v>44</v>
       </c>
       <c r="F64" t="str">
-        <v>250 g</v>
+        <v>100 g</v>
       </c>
       <c r="G64">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H64">
-        <v>620</v>
+        <v>436</v>
       </c>
       <c r="I64" t="str">
-        <v>https://images.unsplash.com/photo-1599490659213-e2b9527bd087?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/063_Sakthi_Coriander_Powder.jpg</v>
       </c>
       <c r="J64" t="str">
-        <v>Paper-thin slices of mature Nendran plantains fried golden in pure fragrant cold-pressed coconut oil with sea salt and turmeric.</v>
+        <v>Sakthi Dhaniya powder with fresh roasted coriander seed aroma.</v>
       </c>
       <c r="K64" t="str">
-        <v>Signature crunchy snap. Sourced straight from Thrissur, Kerala. Completely fresh batch.</v>
+        <v>Thickens curries and lends irresistible natural aroma.</v>
       </c>
       <c r="L64" t="str">
         <v>In Stock</v>
@@ -2836,16 +2836,16 @@
         <v>GS-1064</v>
       </c>
       <c r="B65" t="str">
-        <v>Spicy Roasted Makhana (Foxnuts / Lotus Seeds)</v>
+        <v>Sakthi Sambar Powder</v>
       </c>
       <c r="C65" t="str">
-        <v>Heritage Crisps &amp; Snacks</v>
+        <v>Sakthi &amp; Other Cooking Masalas</v>
       </c>
       <c r="D65">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="E65">
-        <v>195</v>
+        <v>50</v>
       </c>
       <c r="F65" t="str">
         <v>100 g</v>
@@ -2854,16 +2854,16 @@
         <v>4.8</v>
       </c>
       <c r="H65">
-        <v>215</v>
+        <v>93</v>
       </c>
       <c r="I65" t="str">
-        <v>https://images.unsplash.com/photo-1599490659213-e2b9527bd087?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/064_Sakthi_Sambar_Powder.jpg</v>
       </c>
       <c r="J65" t="str">
-        <v>Fluffy giant lotus seeds slow-roasted in pure cow ghee and tossed in tangy chaat masala and rock salt.</v>
+        <v>Famous Sakthi Sambar Podi with the signature taste of Tamil Nadu weddings.</v>
       </c>
       <c r="K65" t="str">
-        <v>Low calorie, high calcium, gluten-free super-snack. Ideal evening companion with green tea.</v>
+        <v>Perfect blend of roasted lentils, chillies, cumin, and curry leaves.</v>
       </c>
       <c r="L65" t="str">
         <v>In Stock</v>
@@ -2874,34 +2874,34 @@
         <v>GS-1065</v>
       </c>
       <c r="B66" t="str">
-        <v>Butter Murukku / Thenkuzhal (Melt-in-Mouth)</v>
+        <v>Sakthi Rasam Powder</v>
       </c>
       <c r="C66" t="str">
-        <v>Heritage Crisps &amp; Snacks</v>
+        <v>Sakthi &amp; Other Cooking Masalas</v>
       </c>
       <c r="D66">
+        <v>40</v>
+      </c>
+      <c r="E66">
+        <v>48</v>
+      </c>
+      <c r="F66" t="str">
+        <v>100 g</v>
+      </c>
+      <c r="G66">
+        <v>4.6</v>
+      </c>
+      <c r="H66">
         <v>110</v>
       </c>
-      <c r="E66">
-        <v>135</v>
-      </c>
-      <c r="F66" t="str">
-        <v>200 g</v>
-      </c>
-      <c r="G66">
-        <v>4.9</v>
-      </c>
-      <c r="H66">
-        <v>340</v>
-      </c>
       <c r="I66" t="str">
-        <v>https://images.unsplash.com/photo-1599490659213-e2b9527bd087?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/065_Sakthi_Rasam_Powder.jpg</v>
       </c>
       <c r="J66" t="str">
-        <v>Fragrant rice and roasted gram coils enriched with white farm butter and cumin seeds. Incredibly delicate crunch.</v>
+        <v>Sakthi spicy pepper rasam powder for steaming digestive rasam sadam.</v>
       </c>
       <c r="K66" t="str">
-        <v>Handmade by village women artisans in Manapparai. Traditional festive comfort snack.</v>
+        <v>Laden with black pepper, cumin, garlic, and coriander.</v>
       </c>
       <c r="L66" t="str">
         <v>In Stock</v>
@@ -2912,34 +2912,34 @@
         <v>GS-1066</v>
       </c>
       <c r="B67" t="str">
-        <v>Pepper Roasted Split Cashews (Hot &amp; Savory)</v>
+        <v>Sakthi Chicken Masala</v>
       </c>
       <c r="C67" t="str">
-        <v>Heritage Crisps &amp; Snacks</v>
+        <v>Sakthi &amp; Other Cooking Masalas</v>
       </c>
       <c r="D67">
-        <v>240</v>
+        <v>45</v>
       </c>
       <c r="E67">
-        <v>290</v>
+        <v>55</v>
       </c>
       <c r="F67" t="str">
-        <v>150 g</v>
+        <v>100 g</v>
       </c>
       <c r="G67">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H67">
-        <v>180</v>
+        <v>127</v>
       </c>
       <c r="I67" t="str">
-        <v>https://images.unsplash.com/photo-1509358271058-acd22cc93898?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/066_Sakthi_Chicken_Masala.jpg</v>
       </c>
       <c r="J67" t="str">
-        <v>Plump Goan cashew halves roasted with crushed Malabar black pepper and curry leaf crisps.</v>
+        <v>Sakthi Chicken Masala for authentic Southern village-style chicken gravy.</v>
       </c>
       <c r="K67" t="str">
-        <v>Dry roasted with pure ghee and coarse sea salt. Irresistibly savory treat.</v>
+        <v>Packed with aromatic whole spices ground under controlled temperatures.</v>
       </c>
       <c r="L67" t="str">
         <v>In Stock</v>
@@ -2950,34 +2950,34 @@
         <v>GS-1067</v>
       </c>
       <c r="B68" t="str">
-        <v>Organic Proso Millet (Cheena Raw)</v>
+        <v>Sakthi Mutton Masala</v>
       </c>
       <c r="C68" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Sakthi &amp; Other Cooking Masalas</v>
       </c>
       <c r="D68">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="E68">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="F68" t="str">
-        <v>500 g</v>
+        <v>100 g</v>
       </c>
       <c r="G68">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H68">
-        <v>363</v>
+        <v>144</v>
       </c>
       <c r="I68" t="str">
-        <v>https://images.unsplash.com/photo-1586201375761-83865001e31c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/067_Sakthi_Mutton_Masala.jpg</v>
       </c>
       <c r="J68" t="str">
-        <v>High protein ancient millet for nutritious upma and grain bowls.</v>
+        <v>Rich spicy mutton gravy masala for tender meat gravies and sukka.</v>
       </c>
       <c r="K68" t="str">
-        <v>Gluten-free, zero chemical polish.</v>
+        <v>Selected aromatic cloves, cinnamon, cardamom, and roasted spices.</v>
       </c>
       <c r="L68" t="str">
         <v>In Stock</v>
@@ -2988,34 +2988,34 @@
         <v>GS-1068</v>
       </c>
       <c r="B69" t="str">
-        <v>Red Poha / Flattened Rice (Thick)</v>
+        <v>Sakthi Garam Masala</v>
       </c>
       <c r="C69" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Sakthi &amp; Other Cooking Masalas</v>
       </c>
       <c r="D69">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E69">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="F69" t="str">
-        <v>1 kg</v>
+        <v>100 g</v>
       </c>
       <c r="G69">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H69">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="I69" t="str">
-        <v>https://images.unsplash.com/photo-1586201375761-83865001e31c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/068_Sakthi_Garam_Masala.jpg</v>
       </c>
       <c r="J69" t="str">
-        <v>Nutritious iron-rich flattened red rice for wholesome quick breakfasts.</v>
+        <v>Premium blend of roasted warm spices to finish off delicious curries.</v>
       </c>
       <c r="K69" t="str">
-        <v>Iron powerhouse, naturally sun-dried.</v>
+        <v>All-natural aromatic spice mix with no artificial fillers.</v>
       </c>
       <c r="L69" t="str">
         <v>In Stock</v>
@@ -3026,34 +3026,34 @@
         <v>GS-1069</v>
       </c>
       <c r="B70" t="str">
-        <v>White Poha / Aval (Medium Thick)</v>
+        <v>Sakthi Pepper Powder</v>
       </c>
       <c r="C70" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Sakthi &amp; Other Cooking Masalas</v>
       </c>
       <c r="D70">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E70">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F70" t="str">
-        <v>1 kg</v>
+        <v>100 g</v>
       </c>
       <c r="G70">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H70">
-        <v>376</v>
+        <v>178</v>
       </c>
       <c r="I70" t="str">
-        <v>https://images.unsplash.com/photo-1586201375761-83865001e31c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/069_Sakthi_Pepper_Powder.jpg</v>
       </c>
       <c r="J70" t="str">
-        <v>Delicate beaten rice flakes that absorb spices and coconut milk beautifully.</v>
+        <v>Crushed pure black pepper powder, spicy and therapeutic.</v>
       </c>
       <c r="K70" t="str">
-        <v>Quick cooking, light on stomach.</v>
+        <v>Fine powdered high-pungency black peppercorns.</v>
       </c>
       <c r="L70" t="str">
         <v>In Stock</v>
@@ -3064,34 +3064,34 @@
         <v>GS-1070</v>
       </c>
       <c r="B71" t="str">
-        <v>Ancient Emmer Khapli Wheat Grain</v>
+        <v>Sakthi Biryani Masala</v>
       </c>
       <c r="C71" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Sakthi &amp; Other Cooking Masalas</v>
       </c>
       <c r="D71">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="E71">
-        <v>230</v>
+        <v>65</v>
       </c>
       <c r="F71" t="str">
-        <v>1 kg</v>
+        <v>100 g</v>
       </c>
       <c r="G71">
         <v>4.8</v>
       </c>
       <c r="H71">
-        <v>364</v>
+        <v>195</v>
       </c>
       <c r="I71" t="str">
-        <v>https://images.unsplash.com/photo-1586201375761-83865001e31c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/070_Sakthi_Biryani_Masala.jpg</v>
       </c>
       <c r="J71" t="str">
-        <v>Diabetic-friendly ancient heirloom low-gluten wheat grain.</v>
+        <v>Fragrant biryani masala mix for dum biryani and kuska with royal scent.</v>
       </c>
       <c r="K71" t="str">
-        <v>Low GI, rich in beta glucans and minerals.</v>
+        <v>Rich in star anise, mace, cardamom, and clove essence.</v>
       </c>
       <c r="L71" t="str">
         <v>In Stock</v>
@@ -3102,34 +3102,34 @@
         <v>GS-1071</v>
       </c>
       <c r="B72" t="str">
-        <v>Steel Cut Organic Oats</v>
+        <v>Sakthi Kulambu Chilli Powder</v>
       </c>
       <c r="C72" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Sakthi &amp; Other Cooking Masalas</v>
       </c>
       <c r="D72">
-        <v>175</v>
+        <v>45</v>
       </c>
       <c r="E72">
-        <v>210</v>
+        <v>52</v>
       </c>
       <c r="F72" t="str">
-        <v>1 kg</v>
+        <v>100 g</v>
       </c>
       <c r="G72">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H72">
-        <v>86</v>
+        <v>212</v>
       </c>
       <c r="I72" t="str">
-        <v>https://images.unsplash.com/photo-1586201375761-83865001e31c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/071_Sakthi_Kulambu_Chilli_Powder.jpg</v>
       </c>
       <c r="J72" t="str">
-        <v>Coarsely chopped whole oat groats for hearty chewy porridge.</v>
+        <v>All-in-one Kulambu Milagai Thool for authentic Vatha Kuzhambu and Meen Kuzhambu.</v>
       </c>
       <c r="K72" t="str">
-        <v>Unprocessed whole kernel.</v>
+        <v>Traditional home-style combo of chilli, coriander, and curry spices.</v>
       </c>
       <c r="L72" t="str">
         <v>In Stock</v>
@@ -3140,16 +3140,16 @@
         <v>GS-1072</v>
       </c>
       <c r="B73" t="str">
-        <v>Seeraga Samba Aromatic Rice</v>
+        <v>Basmati Rice</v>
       </c>
       <c r="C73" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Rice</v>
       </c>
       <c r="D73">
-        <v>195</v>
+        <v>145</v>
       </c>
       <c r="E73">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="F73" t="str">
         <v>1 kg</v>
@@ -3158,16 +3158,16 @@
         <v>4.7</v>
       </c>
       <c r="H73">
-        <v>277</v>
+        <v>229</v>
       </c>
       <c r="I73" t="str">
-        <v>https://images.unsplash.com/photo-1586201375761-83865001e31c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/072_Basmati_Rice.jpg</v>
       </c>
       <c r="J73" t="str">
-        <v>Tiny aromatic southern pearl rice revered for Dindigul biryani.</v>
+        <v>Long-grain aromatic royal Basmati rice with slender grains that fluff upon cooking.</v>
       </c>
       <c r="K73" t="str">
-        <v>Distinct earthy fragrance and easy digestion.</v>
+        <v>Aged 12 months, non-sticky and fragrant for special biryanis.</v>
       </c>
       <c r="L73" t="str">
         <v>In Stock</v>
@@ -3178,34 +3178,34 @@
         <v>GS-1073</v>
       </c>
       <c r="B74" t="str">
-        <v>Bamboo Rice (Moongil Arisi)</v>
+        <v>Ponni Raw Rice</v>
       </c>
       <c r="C74" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Rice</v>
       </c>
       <c r="D74">
-        <v>320</v>
+        <v>62</v>
       </c>
       <c r="E74">
-        <v>390</v>
+        <v>72</v>
       </c>
       <c r="F74" t="str">
-        <v>500 g</v>
+        <v>1 kg</v>
       </c>
       <c r="G74">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="H74">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="I74" t="str">
-        <v>https://images.unsplash.com/photo-1586201375761-83865001e31c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/073_Ponni_Raw_Rice.jpg</v>
       </c>
       <c r="J74" t="str">
-        <v>Rare forest seed harvested from dried flowering bamboo trees.</v>
+        <v>Fine white Ponni Pacharisi for steaming hot white rice, pongal, and tiffin.</v>
       </c>
       <c r="K74" t="str">
-        <v>High protein, joint vitality tonic.</v>
+        <v>Directly sourced from Thanjavur Kaveri delta paddy fields.</v>
       </c>
       <c r="L74" t="str">
         <v>In Stock</v>
@@ -3216,34 +3216,34 @@
         <v>GS-1074</v>
       </c>
       <c r="B75" t="str">
-        <v>Karuppu Kavuni Black Forbidden Rice</v>
+        <v>Ponni Boiled Rice</v>
       </c>
       <c r="C75" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Rice</v>
       </c>
       <c r="D75">
-        <v>210</v>
+        <v>65</v>
       </c>
       <c r="E75">
-        <v>260</v>
+        <v>75</v>
       </c>
       <c r="F75" t="str">
         <v>1 kg</v>
       </c>
       <c r="G75">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H75">
-        <v>48</v>
+        <v>263</v>
       </c>
       <c r="I75" t="str">
-        <v>https://images.unsplash.com/photo-1586201375761-83865001e31c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/074_Ponni_Boiled_Rice.jpg</v>
       </c>
       <c r="J75" t="str">
-        <v>Jet-black royal rice loaded with high anthocyanin antioxidants.</v>
+        <v>Traditional single-boiled Ponni Puzhungal Arisi, easy on digestion and nutritious.</v>
       </c>
       <c r="K75" t="str">
-        <v>Sweet nutty fragrance, deep purple hue.</v>
+        <v>Parboiled with husk to retain B-vitamins; firm texture.</v>
       </c>
       <c r="L75" t="str">
         <v>In Stock</v>
@@ -3254,34 +3254,34 @@
         <v>GS-1075</v>
       </c>
       <c r="B76" t="str">
-        <v>Organic Pearl Barley Grains</v>
+        <v>Idli Rice</v>
       </c>
       <c r="C76" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Rice</v>
       </c>
       <c r="D76">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="E76">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="F76" t="str">
-        <v>500 g</v>
+        <v>1 kg</v>
       </c>
       <c r="G76">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H76">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="I76" t="str">
-        <v>https://images.unsplash.com/photo-1586201375761-83865001e31c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/075_Idli_Rice.jpg</v>
       </c>
       <c r="J76" t="str">
-        <v>Cooling mountain barley for restorative soups and detox water.</v>
+        <v>Special short plump Idli Gundu Arisi for feather-soft idlis and crispy dosas.</v>
       </c>
       <c r="K76" t="str">
-        <v>High soluble fiber content.</v>
+        <v>High fermentation yield, clean and stones-free sorted grains.</v>
       </c>
       <c r="L76" t="str">
         <v>In Stock</v>
@@ -3292,34 +3292,34 @@
         <v>GS-1076</v>
       </c>
       <c r="B77" t="str">
-        <v>Broken Wheat Dalia (Lapsi Rava)</v>
+        <v>Sona Masoori Rice</v>
       </c>
       <c r="C77" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Rice</v>
       </c>
       <c r="D77">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E77">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="F77" t="str">
         <v>1 kg</v>
       </c>
       <c r="G77">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H77">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="I77" t="str">
-        <v>https://images.unsplash.com/photo-1586201375761-83865001e31c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/076_Sona_Masoori_Rice.jpg</v>
       </c>
       <c r="J77" t="str">
-        <v>Golden crushed wheat groats for breakfast khichdi and sweet lapsi.</v>
+        <v>Lightweight, aromatic medium-grain rice suitable for everyday South Indian meals.</v>
       </c>
       <c r="K77" t="str">
-        <v>High dietary fiber, zero refined starch.</v>
+        <v>Aged unpolished rice, starch-balanced and light on the belly.</v>
       </c>
       <c r="L77" t="str">
         <v>In Stock</v>
@@ -3330,34 +3330,34 @@
         <v>GS-1077</v>
       </c>
       <c r="B78" t="str">
-        <v>Organic Foxtail Millet Flour (Thinai Atta)</v>
+        <v>Seeraga Samba Rice</v>
       </c>
       <c r="C78" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Rice</v>
       </c>
       <c r="D78">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="E78">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="F78" t="str">
-        <v>500 g</v>
+        <v>1 kg</v>
       </c>
       <c r="G78">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H78">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="I78" t="str">
-        <v>https://images.unsplash.com/photo-1586201375761-83865001e31c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/077_Seeraga_Samba_Rice.jpg</v>
       </c>
       <c r="J78" t="str">
-        <v>Finely milled millet flour for diabetic rotis, dosas, and cookies.</v>
+        <v>Heirloom tiny aromatic rice grain, the soul of authentic Dindigul &amp; Thalappakatti biryani.</v>
       </c>
       <c r="K78" t="str">
-        <v>100% natural, stone ground.</v>
+        <v>Native Tamil Nadu variety with rich aroma and tender bite.</v>
       </c>
       <c r="L78" t="str">
         <v>In Stock</v>
@@ -3368,34 +3368,34 @@
         <v>GS-1078</v>
       </c>
       <c r="B79" t="str">
-        <v>Sorghum Flour (Jowar Atta)</v>
+        <v>Brown Rice</v>
       </c>
       <c r="C79" t="str">
-        <v>Grains, Rice &amp; Millets</v>
+        <v>Rice</v>
       </c>
       <c r="D79">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E79">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F79" t="str">
         <v>1 kg</v>
       </c>
       <c r="G79">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H79">
-        <v>60</v>
+        <v>331</v>
       </c>
       <c r="I79" t="str">
-        <v>https://images.unsplash.com/photo-1586201375761-83865001e31c?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/078_Brown_Rice.jpg</v>
       </c>
       <c r="J79" t="str">
-        <v>Naturally gluten-free stone-ground jowar flour for soft bhakris.</v>
+        <v>Whole grain brown rice with nutritious bran layer intact, high in dietary fiber.</v>
       </c>
       <c r="K79" t="str">
-        <v>High magnesium and phosphorus.</v>
+        <v>Low glycemic index, ideal for diabetic-friendly wholesome diets.</v>
       </c>
       <c r="L79" t="str">
         <v>In Stock</v>
@@ -3406,34 +3406,34 @@
         <v>GS-1079</v>
       </c>
       <c r="B80" t="str">
-        <v>Organic Moth Beans (Matki)</v>
+        <v>Broken Rice</v>
       </c>
       <c r="C80" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Rice</v>
       </c>
       <c r="D80">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E80">
-        <v>150</v>
+        <v>52</v>
       </c>
       <c r="F80" t="str">
         <v>1 kg</v>
       </c>
       <c r="G80">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H80">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="I80" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/079_Broken_Rice.jpg</v>
       </c>
       <c r="J80" t="str">
-        <v>Small earthy brown beans that sprout vigorously for Maharashtrian Misal.</v>
+        <v>Kaikuthal broken rice (Kuruva / Arisi Noi) for delicious upma, kanji, and payasam.</v>
       </c>
       <c r="K80" t="str">
-        <v>Rich in zinc and dietary fiber.</v>
+        <v>Clean sorted broken rice grains that cook quickly.</v>
       </c>
       <c r="L80" t="str">
         <v>In Stock</v>
@@ -3444,34 +3444,34 @@
         <v>GS-1080</v>
       </c>
       <c r="B81" t="str">
-        <v>Split Green Moong Chilka</v>
+        <v>Sampoo / Shampoo</v>
       </c>
       <c r="C81" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Cleaning Products</v>
       </c>
       <c r="D81">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="E81">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="F81" t="str">
-        <v>1 kg</v>
+        <v>180 ml</v>
       </c>
       <c r="G81">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H81">
-        <v>319</v>
+        <v>365</v>
       </c>
       <c r="I81" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/080_Sampoo___Shampoo.jpg</v>
       </c>
       <c r="J81" t="str">
-        <v>Split moong with skin intact for fiber-rich soothing home dals.</v>
+        <v>All-purpose cleansing hair shampoo with foaming bubbles and sweet fragrance.</v>
       </c>
       <c r="K81" t="str">
-        <v>Retains natural mineral outer layer.</v>
+        <v>Gentle daily scalp cleanser for all hair types.</v>
       </c>
       <c r="L81" t="str">
         <v>In Stock</v>
@@ -3482,34 +3482,34 @@
         <v>GS-1081</v>
       </c>
       <c r="B82" t="str">
-        <v>Black Eyed Peas (Lobia / Karamani)</v>
+        <v>Cleaning Plus Floor Cleaner</v>
       </c>
       <c r="C82" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Cleaning Products</v>
       </c>
       <c r="D82">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E82">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F82" t="str">
-        <v>1 kg</v>
+        <v>1 L</v>
       </c>
       <c r="G82">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H82">
-        <v>256</v>
+        <v>382</v>
       </c>
       <c r="I82" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/081_Cleaning_Plus_Floor_Cleaner.jpg</v>
       </c>
       <c r="J82" t="str">
-        <v>Sweet cream-colored beans with black eye, cooks fast without soaking.</v>
+        <v>Disinfectant floor cleaner with fresh pine &amp; floral scent that repels insects.</v>
       </c>
       <c r="K82" t="str">
-        <v>High protein, versatile in curries.</v>
+        <v>Removes greasy floor stains and leaves tile surfaces shining.</v>
       </c>
       <c r="L82" t="str">
         <v>In Stock</v>
@@ -3520,34 +3520,34 @@
         <v>GS-1082</v>
       </c>
       <c r="B83" t="str">
-        <v>Brown Cowpeas (Thattai Payaru)</v>
+        <v>Phenyl / Floor Cleaner</v>
       </c>
       <c r="C83" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Cleaning Products</v>
       </c>
       <c r="D83">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="E83">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="F83" t="str">
-        <v>1 kg</v>
+        <v>1 L</v>
       </c>
       <c r="G83">
         <v>4.7</v>
       </c>
       <c r="H83">
-        <v>129</v>
+        <v>399</v>
       </c>
       <c r="I83" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/082_Phenyl___Floor_Cleaner.jpg</v>
       </c>
       <c r="J83" t="str">
-        <v>Traditional rustic south Indian cowpea with deep savory flavor.</v>
+        <v>Traditional white pine phenyl disinfectant for sanitary cleaning and hygiene.</v>
       </c>
       <c r="K83" t="str">
-        <v>Ideal for spicy kozhambu and sundal.</v>
+        <v>Strong deodorizing action for bathrooms, floors, and drains.</v>
       </c>
       <c r="L83" t="str">
         <v>In Stock</v>
@@ -3558,34 +3558,34 @@
         <v>GS-1083</v>
       </c>
       <c r="B84" t="str">
-        <v>Organic Soya Chunks (High Protein)</v>
+        <v>Lizol Floor Cleaner</v>
       </c>
       <c r="C84" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Cleaning Products</v>
       </c>
       <c r="D84">
-        <v>85</v>
+        <v>195</v>
       </c>
       <c r="E84">
-        <v>105</v>
+        <v>230</v>
       </c>
       <c r="F84" t="str">
-        <v>400 g</v>
+        <v>1 L</v>
       </c>
       <c r="G84">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H84">
-        <v>257</v>
+        <v>416</v>
       </c>
       <c r="I84" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/083_Lizol_Floor_Cleaner.jpg</v>
       </c>
       <c r="J84" t="str">
-        <v>Plant-based super nuggets containing 52% pure vegan protein.</v>
+        <v>Lizol 3-in-1 surface cleaner that kills 99.9% germs with refreshing citrus scent.</v>
       </c>
       <c r="K84" t="str">
-        <v>Textured defatted soy flour.</v>
+        <v>Safe on marble, granite, ceramic tiles, and wooden floors.</v>
       </c>
       <c r="L84" t="str">
         <v>In Stock</v>
@@ -3596,34 +3596,34 @@
         <v>GS-1084</v>
       </c>
       <c r="B85" t="str">
-        <v>Split Bengal Gram (Chana Dal)</v>
+        <v>Harpic Toilet Cleaner</v>
       </c>
       <c r="C85" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Cleaning Products</v>
       </c>
       <c r="D85">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="E85">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="F85" t="str">
-        <v>1 kg</v>
+        <v>1 L</v>
       </c>
       <c r="G85">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H85">
-        <v>119</v>
+        <v>433</v>
       </c>
       <c r="I85" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/084_Harpic_Toilet_Cleaner.jpg</v>
       </c>
       <c r="J85" t="str">
-        <v>Bright golden polished-free split chickpea dal for vada and puran poli.</v>
+        <v>Harpic Power Plus thick liquid that removes 100% limescale and yellow stains.</v>
       </c>
       <c r="K85" t="str">
-        <v>Rich in complex slow carbs.</v>
+        <v>Kills 99.9% toilet germs, leaving sparkling clean ceramic bowls.</v>
       </c>
       <c r="L85" t="str">
         <v>In Stock</v>
@@ -3634,34 +3634,34 @@
         <v>GS-1085</v>
       </c>
       <c r="B86" t="str">
-        <v>Kashmiri White Rajma</v>
+        <v>Domex Toilet Cleaner</v>
       </c>
       <c r="C86" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Cleaning Products</v>
       </c>
       <c r="D86">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="E86">
-        <v>255</v>
+        <v>205</v>
       </c>
       <c r="F86" t="str">
-        <v>1 kg</v>
+        <v>1 L</v>
       </c>
       <c r="G86">
         <v>4.6</v>
       </c>
       <c r="H86">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="I86" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/085_Domex_Toilet_Cleaner.jpg</v>
       </c>
       <c r="J86" t="str">
-        <v>Soft, melt-in-mouth small white kidney beans from Pahalgam valley.</v>
+        <v>Domex fresh guard toilet disinfectant with sodium hypochlorite power.</v>
       </c>
       <c r="K86" t="str">
-        <v>Velvety texture in tomato gravy.</v>
+        <v>Prevents limescale buildup and bad odour for up to 72 hours.</v>
       </c>
       <c r="L86" t="str">
         <v>In Stock</v>
@@ -3672,34 +3672,34 @@
         <v>GS-1086</v>
       </c>
       <c r="B87" t="str">
-        <v>Panchmel Mixed 5-Dal Blend</v>
+        <v>Vim / Dishwash Liquid</v>
       </c>
       <c r="C87" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Cleaning Products</v>
       </c>
       <c r="D87">
         <v>160</v>
       </c>
       <c r="E87">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F87" t="str">
-        <v>1 kg</v>
+        <v>750 ml</v>
       </c>
       <c r="G87">
         <v>4.8</v>
       </c>
       <c r="H87">
-        <v>231</v>
+        <v>107</v>
       </c>
       <c r="I87" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/086_Vim___Dishwash_Liquid.jpg</v>
       </c>
       <c r="J87" t="str">
-        <v>Rajasthani royal mix of Toor, Moong, Chana, Masoor, and Urad dals.</v>
+        <v>Vim Lemon concentrated dishwash gel bottle with easy-pour nozzle.</v>
       </c>
       <c r="K87" t="str">
-        <v>Complete balanced amino acid profile.</v>
+        <v>Cuts through oily curry stains with just a few drops in water.</v>
       </c>
       <c r="L87" t="str">
         <v>In Stock</v>
@@ -3710,34 +3710,34 @@
         <v>GS-1087</v>
       </c>
       <c r="B88" t="str">
-        <v>Organic Green Peas Dried (Vatana)</v>
+        <v>Colin Glass Cleaner</v>
       </c>
       <c r="C88" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Cleaning Products</v>
       </c>
       <c r="D88">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="E88">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F88" t="str">
-        <v>1 kg</v>
+        <v>500 ml</v>
       </c>
       <c r="G88">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H88">
-        <v>240</v>
+        <v>124</v>
       </c>
       <c r="I88" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/087_Colin_Glass_Cleaner.jpg</v>
       </c>
       <c r="J88" t="str">
-        <v>Sweet dried field peas for ragda patties, samosa filling, and chaat.</v>
+        <v>Colin multi-surface and glass cleaner spray with shine boosters.</v>
       </c>
       <c r="K88" t="str">
-        <v>Sun-cured natural whole peas.</v>
+        <v>Leaves streak-free transparent shine on mirrors, windows, and TV screens.</v>
       </c>
       <c r="L88" t="str">
         <v>In Stock</v>
@@ -3748,34 +3748,34 @@
         <v>GS-1088</v>
       </c>
       <c r="B89" t="str">
-        <v>Black Chickpeas Flour (Besan)</v>
+        <v>Dettol Liquid</v>
       </c>
       <c r="C89" t="str">
-        <v>Organic Pulses &amp; Lentils</v>
+        <v>Cleaning Products</v>
       </c>
       <c r="D89">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="E89">
-        <v>120</v>
+        <v>245</v>
       </c>
       <c r="F89" t="str">
-        <v>1 kg</v>
+        <v>500 ml</v>
       </c>
       <c r="G89">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H89">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="I89" t="str">
-        <v>https://images.unsplash.com/photo-1585994192701-f1a505c817ee?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/088_Dettol_Liquid.jpg</v>
       </c>
       <c r="J89" t="str">
-        <v>100% pure chana dal besan with fine silky texture for sweets and pakodas.</v>
+        <v>Dettol Antiseptic Disinfectant liquid for first aid, laundry, and personal hygiene.</v>
       </c>
       <c r="K89" t="str">
-        <v>Zero gluten, zero added cornflour.</v>
+        <v>Doctor-recommended antiseptic protection for complete household care.</v>
       </c>
       <c r="L89" t="str">
         <v>In Stock</v>
@@ -3786,34 +3786,34 @@
         <v>GS-1089</v>
       </c>
       <c r="B90" t="str">
-        <v>Wood-Pressed Safflower Oil (Kardi)</v>
+        <v>Bleaching Powder</v>
       </c>
       <c r="C90" t="str">
-        <v>Cold-Pressed Oils &amp; Pure Ghee</v>
+        <v>Cleaning Products</v>
       </c>
       <c r="D90">
-        <v>380</v>
+        <v>40</v>
       </c>
       <c r="E90">
-        <v>440</v>
+        <v>50</v>
       </c>
       <c r="F90" t="str">
-        <v>1 Litre</v>
+        <v>500 g</v>
       </c>
       <c r="G90">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H90">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="I90" t="str">
-        <v>https://images.unsplash.com/photo-1474979266404-7eaacbcd87c5?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/089_Bleaching_Powder.jpg</v>
       </c>
       <c r="J90" t="str">
-        <v>Light golden heart-friendly oil rich in linoleic polyunsaturated fats.</v>
+        <v>High-grade chlorine bleaching powder for water purification and surface sanitization.</v>
       </c>
       <c r="K90" t="str">
-        <v>Extracted in wooden ghani.</v>
+        <v>Disinfects water tanks, drains, gutters, and outdoor paved pathways.</v>
       </c>
       <c r="L90" t="str">
         <v>In Stock</v>
@@ -3824,34 +3824,34 @@
         <v>GS-1090</v>
       </c>
       <c r="B91" t="str">
-        <v>Cold-Pressed Flaxseed Oil (Linseed)</v>
+        <v>Scrub Sponge</v>
       </c>
       <c r="C91" t="str">
-        <v>Cold-Pressed Oils &amp; Pure Ghee</v>
+        <v>Cleaning Products</v>
       </c>
       <c r="D91">
-        <v>290</v>
+        <v>35</v>
       </c>
       <c r="E91">
-        <v>360</v>
+        <v>45</v>
       </c>
       <c r="F91" t="str">
-        <v>250 ml</v>
+        <v>Pack of 2</v>
       </c>
       <c r="G91">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H91">
-        <v>279</v>
+        <v>175</v>
       </c>
       <c r="I91" t="str">
-        <v>https://images.unsplash.com/photo-1474979266404-7eaacbcd87c5?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/090_Scrub_Sponge.jpg</v>
       </c>
       <c r="J91" t="str">
-        <v>High-potency plant Omega-3 oil bottled raw for dressing and wellness.</v>
+        <v>Dual-sided sponge scrub pad with soft absorbency and abrasive scrubbing side.</v>
       </c>
       <c r="K91" t="str">
-        <v>Cold-pressed below 35°C.</v>
+        <v>Ergonomic foam grip that holds detergent soap lather efficiently.</v>
       </c>
       <c r="L91" t="str">
         <v>In Stock</v>
@@ -3862,34 +3862,34 @@
         <v>GS-1091</v>
       </c>
       <c r="B92" t="str">
-        <v>Pure Cow Butter (Unsalted Makkhan)</v>
+        <v>Broom</v>
       </c>
       <c r="C92" t="str">
-        <v>Cold-Pressed Oils &amp; Pure Ghee</v>
+        <v>Cleaning Products</v>
       </c>
       <c r="D92">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="E92">
-        <v>380</v>
+        <v>120</v>
       </c>
       <c r="F92" t="str">
-        <v>500 g</v>
+        <v>1 piece</v>
       </c>
       <c r="G92">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H92">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="I92" t="str">
-        <v>https://images.unsplash.com/photo-1474979266404-7eaacbcd87c5?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/091_Broom.jpg</v>
       </c>
       <c r="J92" t="str">
-        <v>Farm fresh cultured unsalted butter with sweet grassy pasture aroma.</v>
+        <v>Long durable natural grass / coconut broom for spotless floor sweeping.</v>
       </c>
       <c r="K92" t="str">
-        <v>Crafted from fresh cow milk cream.</v>
+        <v>Flexible sturdy bristles that trap fine dust and hair easily.</v>
       </c>
       <c r="L92" t="str">
         <v>In Stock</v>
@@ -3900,34 +3900,34 @@
         <v>GS-1092</v>
       </c>
       <c r="B93" t="str">
-        <v>Wood-Pressed Castor Oil (Pure Erand)</v>
+        <v>Clinic Plus Shampoo</v>
       </c>
       <c r="C93" t="str">
-        <v>Cold-Pressed Oils &amp; Pure Ghee</v>
+        <v>Personal Care &amp; Shampoo</v>
       </c>
       <c r="D93">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="E93">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="F93" t="str">
-        <v>500 ml</v>
+        <v>180 ml</v>
       </c>
       <c r="G93">
         <v>4.7</v>
       </c>
       <c r="H93">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="I93" t="str">
-        <v>https://images.unsplash.com/photo-1474979266404-7eaacbcd87c5?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/092_Clinic_Plus_Shampoo.jpg</v>
       </c>
       <c r="J93" t="str">
-        <v>Viscous cold-pressed pure castor oil for deep conditioning and ayurvedic care.</v>
+        <v>Clinic Plus Strong &amp; Long shampoo with milk protein formula for strong hair.</v>
       </c>
       <c r="K93" t="str">
-        <v>Hexane-free, virgin grade.</v>
+        <v>Strengthens roots and reduces hair breakage from root to tip.</v>
       </c>
       <c r="L93" t="str">
         <v>In Stock</v>
@@ -3938,34 +3938,34 @@
         <v>GS-1093</v>
       </c>
       <c r="B94" t="str">
-        <v>Wood-Pressed Black Sesame Oil (Til)</v>
+        <v>Sunsilk Shampoo</v>
       </c>
       <c r="C94" t="str">
-        <v>Cold-Pressed Oils &amp; Pure Ghee</v>
+        <v>Personal Care &amp; Shampoo</v>
       </c>
       <c r="D94">
-        <v>440</v>
+        <v>135</v>
       </c>
       <c r="E94">
-        <v>510</v>
+        <v>155</v>
       </c>
       <c r="F94" t="str">
-        <v>1 Litre</v>
+        <v>180 ml</v>
       </c>
       <c r="G94">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H94">
-        <v>368</v>
+        <v>226</v>
       </c>
       <c r="I94" t="str">
-        <v>https://images.unsplash.com/photo-1474979266404-7eaacbcd87c5?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/093_Sunsilk_Shampoo.jpg</v>
       </c>
       <c r="J94" t="str">
-        <v>Dense aromatic pure sesame oil without jaggery for authentic medicinal oiling.</v>
+        <v>Sunsilk Black Shine shampoo co-created with hair experts with Amla-pearl oil.</v>
       </c>
       <c r="K94" t="str">
-        <v>Pure black sesame seed extraction.</v>
+        <v>Locks in deep glossy shine and bouncy softness.</v>
       </c>
       <c r="L94" t="str">
         <v>In Stock</v>
@@ -3976,34 +3976,34 @@
         <v>GS-1094</v>
       </c>
       <c r="B95" t="str">
-        <v>Grass-Fed Cow Colostrum Ghee</v>
+        <v>Head &amp; Shoulders Shampoo</v>
       </c>
       <c r="C95" t="str">
-        <v>Cold-Pressed Oils &amp; Pure Ghee</v>
+        <v>Personal Care &amp; Shampoo</v>
       </c>
       <c r="D95">
-        <v>1650</v>
+        <v>170</v>
       </c>
       <c r="E95">
-        <v>1950</v>
+        <v>199</v>
       </c>
       <c r="F95" t="str">
-        <v>300 ml</v>
+        <v>180 ml</v>
       </c>
       <c r="G95">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H95">
-        <v>315</v>
+        <v>243</v>
       </c>
       <c r="I95" t="str">
-        <v>https://images.unsplash.com/photo-1474979266404-7eaacbcd87c5?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/094_Head_&amp;_Shoulders_Shampoo.jpg</v>
       </c>
       <c r="J95" t="str">
-        <v>Ultra-rare golden elixir clarified from first milk post-calving.</v>
+        <v>Head &amp; Shoulders Cool Menthol anti-dandruff shampoo with icy tingling freshness.</v>
       </c>
       <c r="K95" t="str">
-        <v>Rich in immunoglobulins and growth factors.</v>
+        <v>Clinically proven formula eliminates up to 100% visible dandruff flakes.</v>
       </c>
       <c r="L95" t="str">
         <v>In Stock</v>
@@ -4014,34 +4014,34 @@
         <v>GS-1095</v>
       </c>
       <c r="B96" t="str">
-        <v>Star Anise (Chakra Phool Whole)</v>
+        <v>Dove Shampoo</v>
       </c>
       <c r="C96" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Personal Care &amp; Shampoo</v>
       </c>
       <c r="D96">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E96">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F96" t="str">
-        <v>100 g</v>
+        <v>180 ml</v>
       </c>
       <c r="G96">
         <v>4.6</v>
       </c>
       <c r="H96">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="I96" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/095_Dove_Shampoo.jpg</v>
       </c>
       <c r="J96" t="str">
-        <v>Fragrant eight-pointed licorice spice essential for authentic biryani.</v>
+        <v>Dove Daily Moisture shampoo with Pro-Moisture complex for smooth silky locks.</v>
       </c>
       <c r="K96" t="str">
-        <v>Whole intact hand-selected stars.</v>
+        <v>Protects normal hair from everyday environmental wear and tear.</v>
       </c>
       <c r="L96" t="str">
         <v>In Stock</v>
@@ -4052,34 +4052,34 @@
         <v>GS-1096</v>
       </c>
       <c r="B97" t="str">
-        <v>Kerala Whole Cloves (Laung)</v>
+        <v>Parachute Coconut Oil</v>
       </c>
       <c r="C97" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Personal Care &amp; Shampoo</v>
       </c>
       <c r="D97">
-        <v>195</v>
+        <v>88</v>
       </c>
       <c r="E97">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="F97" t="str">
-        <v>100 g</v>
+        <v>200 ml</v>
       </c>
       <c r="G97">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H97">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="I97" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/096_Parachute_Coconut_Oil.jpg</v>
       </c>
       <c r="J97" t="str">
-        <v>High essential-oil cloves with large round unbroken heads.</v>
+        <v>Parachute 100% pure coconut oil made from sun-dried roasted Malabar copra.</v>
       </c>
       <c r="K97" t="str">
-        <v>Origin: Wayanad spice gardens.</v>
+        <v>5-stage filtration process delivers untouched edible-grade coconut nourishment.</v>
       </c>
       <c r="L97" t="str">
         <v>In Stock</v>
@@ -4090,34 +4090,34 @@
         <v>GS-1097</v>
       </c>
       <c r="B98" t="str">
-        <v>Mace Blades (Javitri)</v>
+        <v>Navratna Hair Oil</v>
       </c>
       <c r="C98" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Personal Care &amp; Shampoo</v>
       </c>
       <c r="D98">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="E98">
-        <v>360</v>
+        <v>140</v>
       </c>
       <c r="F98" t="str">
-        <v>50 g</v>
+        <v>200 ml</v>
       </c>
       <c r="G98">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="H98">
-        <v>144</v>
+        <v>294</v>
       </c>
       <c r="I98" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/097_Navratna_Hair_Oil.jpg</v>
       </c>
       <c r="J98" t="str">
-        <v>Lacy scarlet aril of the nutmeg fruit with warm delicate floral aroma.</v>
+        <v>Navratna Ayurvedic cool hair oil with 9 therapeutic herbal ingredients.</v>
       </c>
       <c r="K98" t="str">
-        <v>Hand-harvested in Kerala.</v>
+        <v>Instant relief from stress, tension, headache, and sleeplessness.</v>
       </c>
       <c r="L98" t="str">
         <v>In Stock</v>
@@ -4128,34 +4128,34 @@
         <v>GS-1098</v>
       </c>
       <c r="B99" t="str">
-        <v>Whole Nutmeg with Shell (Jaiphal)</v>
+        <v>Fairness / Face Cream</v>
       </c>
       <c r="C99" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Personal Care &amp; Shampoo</v>
       </c>
       <c r="D99">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="E99">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="F99" t="str">
-        <v>100 g</v>
+        <v>50 g</v>
       </c>
       <c r="G99">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H99">
-        <v>158</v>
+        <v>311</v>
       </c>
       <c r="I99" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/098_Fairness___Face_Cream.jpg</v>
       </c>
       <c r="J99" t="str">
-        <v>Aromatic whole nutmegs that preserve freshness until grated.</v>
+        <v>Daily nourishing face cream with multivitamins for clear glowing skin.</v>
       </c>
       <c r="K99" t="str">
-        <v>Deep woodsy comforting fragrance.</v>
+        <v>Lightweight non-oily formula with SPF protection against sun tan.</v>
       </c>
       <c r="L99" t="str">
         <v>In Stock</v>
@@ -4166,34 +4166,34 @@
         <v>GS-1099</v>
       </c>
       <c r="B100" t="str">
-        <v>Black Cumin Seeds (Shahi Jeera)</v>
+        <v>Toothpaste</v>
       </c>
       <c r="C100" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Personal Care &amp; Shampoo</v>
       </c>
       <c r="D100">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E100">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="F100" t="str">
-        <v>100 g</v>
+        <v>150 g</v>
       </c>
       <c r="G100">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H100">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="I100" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/099_Toothpaste.jpg</v>
       </c>
       <c r="J100" t="str">
-        <v>Slender dark cumin with delicate sweet caraway undertones.</v>
+        <v>Complete oral care fluoride toothpaste for cavity protection and fresh breath.</v>
       </c>
       <c r="K100" t="str">
-        <v>Essential for royal Awadhi cuisine.</v>
+        <v>Strengthens enamel and protects gums against plaque.</v>
       </c>
       <c r="L100" t="str">
         <v>In Stock</v>
@@ -4204,34 +4204,34 @@
         <v>GS-1100</v>
       </c>
       <c r="B101" t="str">
-        <v>Ajwain Seeds (Carom / Omam)</v>
+        <v>Toothbrush</v>
       </c>
       <c r="C101" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Personal Care &amp; Shampoo</v>
       </c>
       <c r="D101">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E101">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="F101" t="str">
-        <v>200 g</v>
+        <v>Pack of 2</v>
       </c>
       <c r="G101">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H101">
-        <v>193</v>
+        <v>345</v>
       </c>
       <c r="I101" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/100_Toothbrush.jpg</v>
       </c>
       <c r="J101" t="str">
-        <v>Digestive powerhouse with strong thyme aroma for breads and fried snacks.</v>
+        <v>Medium zig-zag bristles toothbrush with tongue cleaner for deep dental hygiene.</v>
       </c>
       <c r="K101" t="str">
-        <v>Cleansed and de-stoned.</v>
+        <v>Flexible neck reaches back teeth effortlessly.</v>
       </c>
       <c r="L101" t="str">
         <v>In Stock</v>
@@ -4242,34 +4242,34 @@
         <v>GS-1101</v>
       </c>
       <c r="B102" t="str">
-        <v>Fennel Seeds (Lucknowi Saunf)</v>
+        <v>Bathing Loofah</v>
       </c>
       <c r="C102" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Personal Care &amp; Shampoo</v>
       </c>
       <c r="D102">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="E102">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="F102" t="str">
-        <v>200 g</v>
+        <v>1 piece</v>
       </c>
       <c r="G102">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H102">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="I102" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/101_Bathing_Loofah.jpg</v>
       </c>
       <c r="J102" t="str">
-        <v>Fragrant sweet green small fennel seeds for digestive refreshment.</v>
+        <v>Soft exfoliating mesh body scrubber loofah for luxurious soapy shower foam.</v>
       </c>
       <c r="K102" t="str">
-        <v>Naturally green, non-dyed.</v>
+        <v>Gentle on sensitive skin, removes dead cells and increases blood flow.</v>
       </c>
       <c r="L102" t="str">
         <v>In Stock</v>
@@ -4280,34 +4280,34 @@
         <v>GS-1102</v>
       </c>
       <c r="B103" t="str">
-        <v>Fenugreek Seeds (Methi Dana)</v>
+        <v>Toor Dal</v>
       </c>
       <c r="C103" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D103">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="E103">
-        <v>70</v>
+        <v>185</v>
       </c>
       <c r="F103" t="str">
-        <v>250 g</v>
+        <v>1 kg</v>
       </c>
       <c r="G103">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H103">
-        <v>344</v>
+        <v>379</v>
       </c>
       <c r="I103" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/102_Toor_Dal.jpg</v>
       </c>
       <c r="J103" t="str">
-        <v>Golden bittersweet seeds that enhance sambar, pickles, and idli fermentation.</v>
+        <v>Sun-dried unpolished Toor Dal (Thuvaram Paruppu) with rich nutty aroma.</v>
       </c>
       <c r="K103" t="str">
-        <v>Cleaned machine-sorted grade.</v>
+        <v>High protein, cooks into thick golden sambar and kootu.</v>
       </c>
       <c r="L103" t="str">
         <v>In Stock</v>
@@ -4318,34 +4318,34 @@
         <v>GS-1103</v>
       </c>
       <c r="B104" t="str">
-        <v>Whole Dry Ginger (Sonth)</v>
+        <v>Urad Dal</v>
       </c>
       <c r="C104" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D104">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="E104">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="F104" t="str">
-        <v>150 g</v>
+        <v>1 kg</v>
       </c>
       <c r="G104">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H104">
-        <v>274</v>
+        <v>396</v>
       </c>
       <c r="I104" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/103_Urad_Dal.jpg</v>
       </c>
       <c r="J104" t="str">
-        <v>Unbleached dry ginger root for winter decoctions, tea, and dry spice powders.</v>
+        <v>Whole white unpolished Urad Dal (Ulutham Paruppu) for fluffy idli batter and medu vada.</v>
       </c>
       <c r="K104" t="str">
-        <v>Sun-dried farm ginger root.</v>
+        <v>Excellent batter rising power, high dietary fiber and protein.</v>
       </c>
       <c r="L104" t="str">
         <v>In Stock</v>
@@ -4356,34 +4356,34 @@
         <v>GS-1104</v>
       </c>
       <c r="B105" t="str">
-        <v>Garam Masala Powder (Handcrafted 16-Spices)</v>
+        <v>Moong Dal</v>
       </c>
       <c r="C105" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D105">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E105">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="F105" t="str">
-        <v>100 g</v>
+        <v>1 kg</v>
       </c>
       <c r="G105">
         <v>4.8</v>
       </c>
       <c r="H105">
-        <v>163</v>
+        <v>413</v>
       </c>
       <c r="I105" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/104_Moong_Dal.jpg</v>
       </c>
       <c r="J105" t="str">
-        <v>Artisanal blend of 16 whole spices gently roasted and stone ground.</v>
+        <v>Yellow split Moong Dal (Paasi Paruppu), gentle on stomach and nutrient dense.</v>
       </c>
       <c r="K105" t="str">
-        <v>Zero coriander/chilli padding.</v>
+        <v>Quick cooking lentil for ven pongal, dal tadka, and payasam.</v>
       </c>
       <c r="L105" t="str">
         <v>In Stock</v>
@@ -4394,34 +4394,34 @@
         <v>GS-1105</v>
       </c>
       <c r="B106" t="str">
-        <v>Madras Sambar Podi (Traditional Blend)</v>
+        <v>Chana Dal</v>
       </c>
       <c r="C106" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D106">
+        <v>105</v>
+      </c>
+      <c r="E106">
         <v>125</v>
       </c>
-      <c r="E106">
-        <v>155</v>
-      </c>
       <c r="F106" t="str">
-        <v>200 g</v>
+        <v>1 kg</v>
       </c>
       <c r="G106">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H106">
-        <v>251</v>
+        <v>430</v>
       </c>
       <c r="I106" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/105_Chana_Dal.jpg</v>
       </c>
       <c r="J106" t="str">
-        <v>Authentic grandmother recipe with roasted toor dal, coriander, and Salem turmeric.</v>
+        <v>Golden Bengal Gram dal (Kadalai Paruppu) for crispy masala vadai and chutneys.</v>
       </c>
       <c r="K106" t="str">
-        <v>Gives thick homestyle aroma.</v>
+        <v>Clean stone-sorted grains with rich earthy sweetness.</v>
       </c>
       <c r="L106" t="str">
         <v>In Stock</v>
@@ -4432,34 +4432,34 @@
         <v>GS-1106</v>
       </c>
       <c r="B107" t="str">
-        <v>Chettinad Pepper Rasam Powder</v>
+        <v>Green Gram</v>
       </c>
       <c r="C107" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D107">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E107">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F107" t="str">
-        <v>200 g</v>
+        <v>1 kg</v>
       </c>
       <c r="G107">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H107">
-        <v>184</v>
+        <v>87</v>
       </c>
       <c r="I107" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/106_Green_Gram.jpg</v>
       </c>
       <c r="J107" t="str">
-        <v>Fiery, aromatic rasam mix with whole Malabar pepper, cumin, and curry leaves.</v>
+        <v>Whole green Moong beans (Pachai Payaru) for nutritious sprouting and sundal.</v>
       </c>
       <c r="K107" t="str">
-        <v>Instant soul-soothing broth.</v>
+        <v>100% whole grain with fiber-rich green skin intact.</v>
       </c>
       <c r="L107" t="str">
         <v>In Stock</v>
@@ -4470,34 +4470,34 @@
         <v>GS-1107</v>
       </c>
       <c r="B108" t="str">
-        <v>Idli Podi (Gunpowder with Ghee Aroma)</v>
+        <v>Black Pepper</v>
       </c>
       <c r="C108" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D108">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="E108">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="F108" t="str">
-        <v>200 g</v>
+        <v>100 g</v>
       </c>
       <c r="G108">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H108">
-        <v>355</v>
+        <v>104</v>
       </c>
       <c r="I108" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/107_Black_Pepper.jpg</v>
       </c>
       <c r="J108" t="str">
-        <v>Coarse spicy condiment of roasted urad, chana dal, sesame seeds, and red chillies.</v>
+        <v>Whole bold black peppercorns (Milagu) with pungent aroma and medicinal benefits.</v>
       </c>
       <c r="K108" t="str">
-        <v>Mix with sesame oil or ghee.</v>
+        <v>Sun-dried natural Malabar black pepper.</v>
       </c>
       <c r="L108" t="str">
         <v>In Stock</v>
@@ -4508,34 +4508,34 @@
         <v>GS-1108</v>
       </c>
       <c r="B109" t="str">
-        <v>Kalonji Seeds (Black Onion Seeds)</v>
+        <v>Cumin Seeds</v>
       </c>
       <c r="C109" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D109">
+        <v>65</v>
+      </c>
+      <c r="E109">
         <v>80</v>
-      </c>
-      <c r="E109">
-        <v>100</v>
       </c>
       <c r="F109" t="str">
         <v>100 g</v>
       </c>
       <c r="G109">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H109">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I109" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/108_Cumin_Seeds.jpg</v>
       </c>
       <c r="J109" t="str">
-        <v>Peppery onion-scented black seeds for naan, pickles, and herbal teas.</v>
+        <v>Aromatic Jeera seeds (Seeragam) that crackle in hot oil with warm earthiness.</v>
       </c>
       <c r="K109" t="str">
-        <v>Pure Nigella sativa seeds.</v>
+        <v>Essential spice for digestive rasam, tadka, and jeera rice.</v>
       </c>
       <c r="L109" t="str">
         <v>In Stock</v>
@@ -4546,34 +4546,34 @@
         <v>GS-1109</v>
       </c>
       <c r="B110" t="str">
-        <v>White Sesame Seeds (Safed Til)</v>
+        <v>Mustard Seeds</v>
       </c>
       <c r="C110" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D110">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="E110">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="F110" t="str">
-        <v>200 g</v>
+        <v>100 g</v>
       </c>
       <c r="G110">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H110">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="I110" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/109_Mustard_Seeds.jpg</v>
       </c>
       <c r="J110" t="str">
-        <v>Nutty hulled white sesame seeds for winter sweets, tahini, and baking.</v>
+        <v>Small pungent black mustard seeds (Kadugu) for traditional South Indian tempering.</v>
       </c>
       <c r="K110" t="str">
-        <v>Machine-cleaned uniform seeds.</v>
+        <v>Pops vigorously in hot oil to release pungent nutty aroma.</v>
       </c>
       <c r="L110" t="str">
         <v>In Stock</v>
@@ -4584,34 +4584,34 @@
         <v>GS-1110</v>
       </c>
       <c r="B111" t="str">
-        <v>Dry Mango Powder (Amchur)</v>
+        <v>Fenugreek</v>
       </c>
       <c r="C111" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D111">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="E111">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="F111" t="str">
-        <v>150 g</v>
+        <v>100 g</v>
       </c>
       <c r="G111">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H111">
-        <v>365</v>
+        <v>155</v>
       </c>
       <c r="I111" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/110_Fenugreek.jpg</v>
       </c>
       <c r="J111" t="str">
-        <v>Sun-dried sour green mangoes ground into a tangy savory seasoning powder.</v>
+        <v>Golden brown Methi seeds (Vendhayam) that lend subtle bitterness and coolness.</v>
       </c>
       <c r="K111" t="str">
-        <v>Zero added citric acid or flour.</v>
+        <v>Essential for idli batter soft texture, vatha kuzhambu, and fish curry.</v>
       </c>
       <c r="L111" t="str">
         <v>In Stock</v>
@@ -4622,34 +4622,34 @@
         <v>GS-1111</v>
       </c>
       <c r="B112" t="str">
-        <v>Kasoori Methi (Dry Fenugreek Leaves)</v>
+        <v>Tamarind</v>
       </c>
       <c r="C112" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D112">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E112">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="F112" t="str">
-        <v>50 g</v>
+        <v>500 g</v>
       </c>
       <c r="G112">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H112">
-        <v>273</v>
+        <v>172</v>
       </c>
       <c r="I112" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/111_Tamarind.jpg</v>
       </c>
       <c r="J112" t="str">
-        <v>Fragrant shade-dried fenugreek leaves from Nagaur, Rajasthan.</v>
+        <v>Seedless sour Country Tamarind (Puli) with deep brown hue and tangy kick.</v>
       </c>
       <c r="K112" t="str">
-        <v>Rub between palms to release aroma.</v>
+        <v>Cleaned and deseeded, gives authentic body to sambar and kuzhambu.</v>
       </c>
       <c r="L112" t="str">
         <v>In Stock</v>
@@ -4660,34 +4660,34 @@
         <v>GS-1112</v>
       </c>
       <c r="B113" t="str">
-        <v>Pure Rock Salt (Sendha Namak Coarse)</v>
+        <v>Salt</v>
       </c>
       <c r="C113" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D113">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="E113">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F113" t="str">
         <v>1 kg</v>
       </c>
       <c r="G113">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H113">
-        <v>242</v>
+        <v>189</v>
       </c>
       <c r="I113" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/112_Salt.jpg</v>
       </c>
       <c r="J113" t="str">
-        <v>Raw uncrushed pink halite crystals for grinders and slow brine cooking.</v>
+        <v>Refined iodized crystal/table salt for everyday culinary seasoning.</v>
       </c>
       <c r="K113" t="str">
-        <v>Mined from Himalayan seams.</v>
+        <v>Vacuum-evaporated pure salt enriched with essential dietary iodine.</v>
       </c>
       <c r="L113" t="str">
         <v>In Stock</v>
@@ -4698,34 +4698,34 @@
         <v>GS-1113</v>
       </c>
       <c r="B114" t="str">
-        <v>Black Salt Granules (Kala Namak)</v>
+        <v>Besan / Gram Flour</v>
       </c>
       <c r="C114" t="str">
-        <v>Spices, Masalas &amp; Seasonings</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D114">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E114">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F114" t="str">
         <v>500 g</v>
       </c>
       <c r="G114">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H114">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="I114" t="str">
-        <v>https://images.unsplash.com/photo-1599940824399-b87987ceb72a?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/113_Besan___Gram_Flour.jpg</v>
       </c>
       <c r="J114" t="str">
-        <v>Mineral volcanic rock salt with sulfurous tang, beloved for chaats and raitas.</v>
+        <v>Pure stone-ground chana dal Kadalai Maavu for golden bhajis, pakoras, and laddu.</v>
       </c>
       <c r="K114" t="str">
-        <v>Traditional kiln-fired salt.</v>
+        <v>Finely milled 100% chana dal flour with no added wheat.</v>
       </c>
       <c r="L114" t="str">
         <v>In Stock</v>
@@ -4736,34 +4736,34 @@
         <v>GS-1114</v>
       </c>
       <c r="B115" t="str">
-        <v>Makhana Jumbo (Raw Foxnuts)</v>
+        <v>Maida</v>
       </c>
       <c r="C115" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D115">
-        <v>280</v>
+        <v>52</v>
       </c>
       <c r="E115">
-        <v>350</v>
+        <v>62</v>
       </c>
       <c r="F115" t="str">
-        <v>250 g</v>
+        <v>1 kg</v>
       </c>
       <c r="G115">
         <v>4.8</v>
       </c>
       <c r="H115">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="I115" t="str">
-        <v>https://images.unsplash.com/photo-1508061253366-f7da158b6d46?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/114_Maida.jpg</v>
       </c>
       <c r="J115" t="str">
-        <v>Snow-white handpicked giant lotus seeds ready to roast at home.</v>
+        <v>Fine all-purpose refined wheat flour for parottas, snacks, and baking.</v>
       </c>
       <c r="K115" t="str">
-        <v>Zero cholesterol, low sodium.</v>
+        <v>Smooth consistency and high stretch elasticity.</v>
       </c>
       <c r="L115" t="str">
         <v>In Stock</v>
@@ -4774,34 +4774,34 @@
         <v>GS-1115</v>
       </c>
       <c r="B116" t="str">
-        <v>Sunflower Seeds (Raw Shelled)</v>
+        <v>Wheat Flour / Atta</v>
       </c>
       <c r="C116" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D116">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="E116">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="F116" t="str">
-        <v>250 g</v>
+        <v>1 kg</v>
       </c>
       <c r="G116">
         <v>4.6</v>
       </c>
       <c r="H116">
-        <v>291</v>
+        <v>240</v>
       </c>
       <c r="I116" t="str">
-        <v>https://images.unsplash.com/photo-1508061253366-f7da158b6d46?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/115_Wheat_Flour___Atta.jpg</v>
       </c>
       <c r="J116" t="str">
-        <v>Nutty mild seeds loaded with Vitamin E and selenium for daily vitality.</v>
+        <v>100% Whole Wheat Chakki Atta for ultra-soft, fluffy phulkas and rotis.</v>
       </c>
       <c r="K116" t="str">
-        <v>Ready to eat or toast.</v>
+        <v>Milled with wheat bran and germ for maximum natural fiber.</v>
       </c>
       <c r="L116" t="str">
         <v>In Stock</v>
@@ -4812,34 +4812,34 @@
         <v>GS-1116</v>
       </c>
       <c r="B117" t="str">
-        <v>Watermelon Seeds (Magaz Raw)</v>
+        <v>Rava / Sooji</v>
       </c>
       <c r="C117" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D117">
-        <v>140</v>
+        <v>38</v>
       </c>
       <c r="E117">
-        <v>175</v>
+        <v>45</v>
       </c>
       <c r="F117" t="str">
-        <v>250 g</v>
+        <v>500 g</v>
       </c>
       <c r="G117">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H117">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="I117" t="str">
-        <v>https://images.unsplash.com/photo-1508061253366-f7da158b6d46?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/116_Rava___Sooji.jpg</v>
       </c>
       <c r="J117" t="str">
-        <v>Creamy tender seeds used for rich Mughlai curries, gravies, and halwas.</v>
+        <v>Roasted wheat semolina (Rava) for fluffy upma, rava dosa, and rich kesari.</v>
       </c>
       <c r="K117" t="str">
-        <v>De-shelled kernel grade.</v>
+        <v>Coarse golden granules that never turn sticky when boiled.</v>
       </c>
       <c r="L117" t="str">
         <v>In Stock</v>
@@ -4850,34 +4850,34 @@
         <v>GS-1117</v>
       </c>
       <c r="B118" t="str">
-        <v>Flax Seeds (Alsi / Linseeds Raw)</v>
+        <v>Vermicelli / Semiya</v>
       </c>
       <c r="C118" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D118">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="E118">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F118" t="str">
-        <v>250 g</v>
+        <v>500 g</v>
       </c>
       <c r="G118">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H118">
-        <v>365</v>
+        <v>274</v>
       </c>
       <c r="I118" t="str">
-        <v>https://images.unsplash.com/photo-1508061253366-f7da158b6d46?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/117_Vermicelli___Semiya.jpg</v>
       </c>
       <c r="J118" t="str">
-        <v>Golden brown whole flax seeds packed with soluble fiber and plant ALA.</v>
+        <v>Hard wheat roasted semiya for delicious breakfast upma and festive payasam.</v>
       </c>
       <c r="K118" t="str">
-        <v>Great roasted for spice podis.</v>
+        <v>Non-sticky, quick-cooking slender vermicelli strands.</v>
       </c>
       <c r="L118" t="str">
         <v>In Stock</v>
@@ -4888,34 +4888,34 @@
         <v>GS-1118</v>
       </c>
       <c r="B119" t="str">
-        <v>Mamra Almonds (Iranian Handpicked)</v>
+        <v>Appalam</v>
       </c>
       <c r="C119" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D119">
-        <v>1100</v>
+        <v>35</v>
       </c>
       <c r="E119">
-        <v>1350</v>
+        <v>42</v>
       </c>
       <c r="F119" t="str">
-        <v>250 g</v>
+        <v>100 g</v>
       </c>
       <c r="G119">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H119">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="I119" t="str">
-        <v>https://images.unsplash.com/photo-1508061253366-f7da158b6d46?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/118_Appalam.jpg</v>
       </c>
       <c r="J119" t="str">
-        <v>Rare organic concave almonds containing over 50% natural almond oil.</v>
+        <v>Traditional Tamil crispy urad dal Appalam that puffs wide in hot oil.</v>
       </c>
       <c r="K119" t="str">
-        <v>Highest natural almond nutrition.</v>
+        <v>Crisp, crunchy, and seasoned with salt and cumin.</v>
       </c>
       <c r="L119" t="str">
         <v>In Stock</v>
@@ -4926,34 +4926,34 @@
         <v>GS-1119</v>
       </c>
       <c r="B120" t="str">
-        <v>Black Seedless Raisins (Kali Kishmish)</v>
+        <v>Pickle</v>
       </c>
       <c r="C120" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D120">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="E120">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="F120" t="str">
-        <v>250 g</v>
+        <v>300 g</v>
       </c>
       <c r="G120">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H120">
-        <v>226</v>
+        <v>308</v>
       </c>
       <c r="I120" t="str">
-        <v>https://images.unsplash.com/photo-1508061253366-f7da158b6d46?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/119_Pickle.jpg</v>
       </c>
       <c r="J120" t="str">
-        <v>Succulent sweet black monukka raisins packed with iron and antioxidants.</v>
+        <v>Tangy spicy mango/lemon pickle (Oorugai) aged in cold-pressed sesame oil.</v>
       </c>
       <c r="K120" t="str">
-        <v>Soak overnight for vitality.</v>
+        <v>Traditional granny recipe with mustard, fenugreek, and fiery chilli.</v>
       </c>
       <c r="L120" t="str">
         <v>In Stock</v>
@@ -4964,840 +4964,42 @@
         <v>GS-1120</v>
       </c>
       <c r="B121" t="str">
-        <v>Brazil Nuts (Selenium Powerhouse)</v>
+        <v>Papad</v>
       </c>
       <c r="C121" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
+        <v>Other Grocery Essentials</v>
       </c>
       <c r="D121">
-        <v>620</v>
+        <v>45</v>
       </c>
       <c r="E121">
-        <v>780</v>
+        <v>55</v>
       </c>
       <c r="F121" t="str">
-        <v>250 g</v>
+        <v>200 g</v>
       </c>
       <c r="G121">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H121">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="I121" t="str">
-        <v>https://images.unsplash.com/photo-1508061253366-f7da158b6d46?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
+        <v>products/120_Papad.jpg</v>
       </c>
       <c r="J121" t="str">
-        <v>Giant crunchy Amazon rainforest nuts; one nut supplies 100% daily selenium.</v>
+        <v>Spicy pepper urad dal papad, sun-dried and ready to roast or fry.</v>
       </c>
       <c r="K121" t="str">
-        <v>Raw, unblanched whole nuts.</v>
+        <v>Spiced with crushed black pepper and hing.</v>
       </c>
       <c r="L121" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v>GS-1121</v>
-      </c>
-      <c r="B122" t="str">
-        <v>Goji Berries (Sun-Dried)</v>
-      </c>
-      <c r="C122" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
-      </c>
-      <c r="D122">
-        <v>340</v>
-      </c>
-      <c r="E122">
-        <v>420</v>
-      </c>
-      <c r="F122" t="str">
-        <v>150 g</v>
-      </c>
-      <c r="G122">
-        <v>4.8</v>
-      </c>
-      <c r="H122">
-        <v>117</v>
-      </c>
-      <c r="I122" t="str">
-        <v>https://images.unsplash.com/photo-1508061253366-f7da158b6d46?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J122" t="str">
-        <v>Himalayan red super-berries rich in carotenoids, zeaxanthin, and Vitamin C.</v>
-      </c>
-      <c r="K122" t="str">
-        <v>Tangy sweet chewy snack.</v>
-      </c>
-      <c r="L122" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v>GS-1122</v>
-      </c>
-      <c r="B123" t="str">
-        <v>Dried Cranberries (Whole Fruit)</v>
-      </c>
-      <c r="C123" t="str">
-        <v>Dry Fruits, Nuts &amp; Seeds</v>
-      </c>
-      <c r="D123">
-        <v>220</v>
-      </c>
-      <c r="E123">
-        <v>280</v>
-      </c>
-      <c r="F123" t="str">
-        <v>200 g</v>
-      </c>
-      <c r="G123">
-        <v>4.8</v>
-      </c>
-      <c r="H123">
-        <v>248</v>
-      </c>
-      <c r="I123" t="str">
-        <v>https://images.unsplash.com/photo-1508061253366-f7da158b6d46?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J123" t="str">
-        <v>Tart sweet ruby red berries for breakfast granolas, salads, and festive cakes.</v>
-      </c>
-      <c r="K123" t="str">
-        <v>Lightly sweetened whole fruit.</v>
-      </c>
-      <c r="L123" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v>GS-1123</v>
-      </c>
-      <c r="B124" t="str">
-        <v>Neem Blossom Organic Honey</v>
-      </c>
-      <c r="C124" t="str">
-        <v>Farm Honey &amp; Country Sugars</v>
-      </c>
-      <c r="D124">
-        <v>460</v>
-      </c>
-      <c r="E124">
-        <v>560</v>
-      </c>
-      <c r="F124" t="str">
-        <v>500 g</v>
-      </c>
-      <c r="G124">
-        <v>4.9</v>
-      </c>
-      <c r="H124">
-        <v>132</v>
-      </c>
-      <c r="I124" t="str">
-        <v>https://images.unsplash.com/photo-1587049352846-4a222e784d38?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J124" t="str">
-        <v>Dark amber honey collected during neem tree flowering season.</v>
-      </c>
-      <c r="K124" t="str">
-        <v>Antibacterial and blood-purifying properties.</v>
-      </c>
-      <c r="L124" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>GS-1124</v>
-      </c>
-      <c r="B125" t="str">
-        <v>Eucalyptus Wild Reserve Honey</v>
-      </c>
-      <c r="C125" t="str">
-        <v>Farm Honey &amp; Country Sugars</v>
-      </c>
-      <c r="D125">
-        <v>390</v>
-      </c>
-      <c r="E125">
-        <v>480</v>
-      </c>
-      <c r="F125" t="str">
-        <v>500 g</v>
-      </c>
-      <c r="G125">
-        <v>4.7</v>
-      </c>
-      <c r="H125">
-        <v>288</v>
-      </c>
-      <c r="I125" t="str">
-        <v>https://images.unsplash.com/photo-1587049352846-4a222e784d38?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J125" t="str">
-        <v>Distinct menthol herbal note honey harvested from Ooty eucalyptus groves.</v>
-      </c>
-      <c r="K125" t="str">
-        <v>Soothes throat irritation and coughs.</v>
-      </c>
-      <c r="L125" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>GS-1125</v>
-      </c>
-      <c r="B126" t="str">
-        <v>Organic Cane Jaggery Block (Bhel Gur)</v>
-      </c>
-      <c r="C126" t="str">
-        <v>Farm Honey &amp; Country Sugars</v>
-      </c>
-      <c r="D126">
-        <v>80</v>
-      </c>
-      <c r="E126">
-        <v>100</v>
-      </c>
-      <c r="F126" t="str">
-        <v>1 kg</v>
-      </c>
-      <c r="G126">
-        <v>4.6</v>
-      </c>
-      <c r="H126">
-        <v>143</v>
-      </c>
-      <c r="I126" t="str">
-        <v>https://images.unsplash.com/photo-1587049352846-4a222e784d38?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J126" t="str">
-        <v>Firm golden block jaggery traditionally prepared in iron pans.</v>
-      </c>
-      <c r="K126" t="str">
-        <v>Rich in iron, potassium, and magnesium.</v>
-      </c>
-      <c r="L126" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>GS-1126</v>
-      </c>
-      <c r="B127" t="str">
-        <v>Coconut Palm Sugar (Low Glycemic)</v>
-      </c>
-      <c r="C127" t="str">
-        <v>Farm Honey &amp; Country Sugars</v>
-      </c>
-      <c r="D127">
-        <v>240</v>
-      </c>
-      <c r="E127">
-        <v>295</v>
-      </c>
-      <c r="F127" t="str">
-        <v>500 g</v>
-      </c>
-      <c r="G127">
-        <v>4.7</v>
-      </c>
-      <c r="H127">
-        <v>81</v>
-      </c>
-      <c r="I127" t="str">
-        <v>https://images.unsplash.com/photo-1587049352846-4a222e784d38?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J127" t="str">
-        <v>Unrefined sugar dehydrated from fresh coconut blossom sap. Mild caramel notes.</v>
-      </c>
-      <c r="K127" t="str">
-        <v>Low GI of 35, sustainable choice.</v>
-      </c>
-      <c r="L127" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>GS-1127</v>
-      </c>
-      <c r="B128" t="str">
-        <v>Raw Khandsari Sugar (Desi Khand)</v>
-      </c>
-      <c r="C128" t="str">
-        <v>Farm Honey &amp; Country Sugars</v>
-      </c>
-      <c r="D128">
-        <v>110</v>
-      </c>
-      <c r="E128">
-        <v>140</v>
-      </c>
-      <c r="F128" t="str">
-        <v>1 kg</v>
-      </c>
-      <c r="G128">
-        <v>4.6</v>
-      </c>
-      <c r="H128">
-        <v>59</v>
-      </c>
-      <c r="I128" t="str">
-        <v>https://images.unsplash.com/photo-1587049352846-4a222e784d38?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J128" t="str">
-        <v>Traditional crystallised unbleached cane sugar rich in natural molasses.</v>
-      </c>
-      <c r="K128" t="str">
-        <v>Chemical-free alternative to table sugar.</v>
-      </c>
-      <c r="L128" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>GS-1128</v>
-      </c>
-      <c r="B129" t="str">
-        <v>Darjeeling First Flush Whole Leaf Tea</v>
-      </c>
-      <c r="C129" t="str">
-        <v>Artisanal Teas &amp; Filter Coffee</v>
-      </c>
-      <c r="D129">
-        <v>420</v>
-      </c>
-      <c r="E129">
-        <v>520</v>
-      </c>
-      <c r="F129" t="str">
-        <v>100 g</v>
-      </c>
-      <c r="G129">
-        <v>4.5</v>
-      </c>
-      <c r="H129">
-        <v>337</v>
-      </c>
-      <c r="I129" t="str">
-        <v>https://images.unsplash.com/photo-1544787219-7f47ccb76574?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J129" t="str">
-        <v>The Champagne of Teas: spring harvested tender shoots with muscatel notes.</v>
-      </c>
-      <c r="K129" t="str">
-        <v>Single estate high-altitude garden.</v>
-      </c>
-      <c r="L129" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>GS-1129</v>
-      </c>
-      <c r="B130" t="str">
-        <v>Assam Golden Tippy CTC Leaf Tea</v>
-      </c>
-      <c r="C130" t="str">
-        <v>Artisanal Teas &amp; Filter Coffee</v>
-      </c>
-      <c r="D130">
-        <v>220</v>
-      </c>
-      <c r="E130">
-        <v>270</v>
-      </c>
-      <c r="F130" t="str">
-        <v>500 g</v>
-      </c>
-      <c r="G130">
-        <v>4.8</v>
-      </c>
-      <c r="H130">
-        <v>320</v>
-      </c>
-      <c r="I130" t="str">
-        <v>https://images.unsplash.com/photo-1544787219-7f47ccb76574?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J130" t="str">
-        <v>Bold brisk full-bodied tea with golden tippy buds for rich morning cup.</v>
-      </c>
-      <c r="K130" t="str">
-        <v>Deep ruby liquor with malty character.</v>
-      </c>
-      <c r="L130" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>GS-1130</v>
-      </c>
-      <c r="B131" t="str">
-        <v>Peppermint &amp; Spearmint Herbal Leaf Tea</v>
-      </c>
-      <c r="C131" t="str">
-        <v>Artisanal Teas &amp; Filter Coffee</v>
-      </c>
-      <c r="D131">
-        <v>190</v>
-      </c>
-      <c r="E131">
-        <v>235</v>
-      </c>
-      <c r="F131" t="str">
-        <v>100 g</v>
-      </c>
-      <c r="G131">
-        <v>4.7</v>
-      </c>
-      <c r="H131">
-        <v>138</v>
-      </c>
-      <c r="I131" t="str">
-        <v>https://images.unsplash.com/photo-1544787219-7f47ccb76574?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J131" t="str">
-        <v>Crisp refreshing pure mint leaves that soothe digestion and freshen breath.</v>
-      </c>
-      <c r="K131" t="str">
-        <v>100% pure dried whole mint leaves.</v>
-      </c>
-      <c r="L131" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>GS-1131</v>
-      </c>
-      <c r="B132" t="str">
-        <v>Pure Roasted Chicory Powder</v>
-      </c>
-      <c r="C132" t="str">
-        <v>Artisanal Teas &amp; Filter Coffee</v>
-      </c>
-      <c r="D132">
-        <v>95</v>
-      </c>
-      <c r="E132">
-        <v>120</v>
-      </c>
-      <c r="F132" t="str">
-        <v>250 g</v>
-      </c>
-      <c r="G132">
-        <v>4.7</v>
-      </c>
-      <c r="H132">
-        <v>258</v>
-      </c>
-      <c r="I132" t="str">
-        <v>https://images.unsplash.com/photo-1544787219-7f47ccb76574?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J132" t="str">
-        <v>French roasted and ground chicory root to customize your own filter coffee blend.</v>
-      </c>
-      <c r="K132" t="str">
-        <v>Rich caramel body and aroma.</v>
-      </c>
-      <c r="L132" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>GS-1132</v>
-      </c>
-      <c r="B133" t="str">
-        <v>Organic Green Tea Whole Leaf (Gunpowder)</v>
-      </c>
-      <c r="C133" t="str">
-        <v>Artisanal Teas &amp; Filter Coffee</v>
-      </c>
-      <c r="D133">
-        <v>210</v>
-      </c>
-      <c r="E133">
-        <v>260</v>
-      </c>
-      <c r="F133" t="str">
-        <v>200 g</v>
-      </c>
-      <c r="G133">
-        <v>4.6</v>
-      </c>
-      <c r="H133">
-        <v>283</v>
-      </c>
-      <c r="I133" t="str">
-        <v>https://images.unsplash.com/photo-1544787219-7f47ccb76574?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J133" t="str">
-        <v>Tightly rolled green tea pearls that unfurl in hot water, loaded with EGCG.</v>
-      </c>
-      <c r="K133" t="str">
-        <v>Gentle grassy freshness without bitterness.</v>
-      </c>
-      <c r="L133" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>GS-1133</v>
-      </c>
-      <c r="B134" t="str">
-        <v>Dry Ginger Coffee Mix (Sukku Kaapi)</v>
-      </c>
-      <c r="C134" t="str">
-        <v>Artisanal Teas &amp; Filter Coffee</v>
-      </c>
-      <c r="D134">
-        <v>160</v>
-      </c>
-      <c r="E134">
-        <v>195</v>
-      </c>
-      <c r="F134" t="str">
-        <v>200 g</v>
-      </c>
-      <c r="G134">
-        <v>4.6</v>
-      </c>
-      <c r="H134">
-        <v>244</v>
-      </c>
-      <c r="I134" t="str">
-        <v>https://images.unsplash.com/photo-1544787219-7f47ccb76574?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J134" t="str">
-        <v>Traditional herbal brew powder with dry ginger, black pepper, coriander, and tulsi.</v>
-      </c>
-      <c r="K134" t="str">
-        <v>Instant immunity tonic with jaggery.</v>
-      </c>
-      <c r="L134" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>GS-1134</v>
-      </c>
-      <c r="B135" t="str">
-        <v>Kara Boondi with Peanuts &amp; Curry Leaves</v>
-      </c>
-      <c r="C135" t="str">
-        <v>Heritage Crisps &amp; Snacks</v>
-      </c>
-      <c r="D135">
-        <v>110</v>
-      </c>
-      <c r="E135">
-        <v>135</v>
-      </c>
-      <c r="F135" t="str">
-        <v>200 g</v>
-      </c>
-      <c r="G135">
-        <v>4.7</v>
-      </c>
-      <c r="H135">
-        <v>362</v>
-      </c>
-      <c r="I135" t="str">
-        <v>https://images.unsplash.com/photo-1599490659213-e2b9527bd087?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J135" t="str">
-        <v>Tiny crispy chickpea pearls fried golden and tossed with roasted nuts.</v>
-      </c>
-      <c r="K135" t="str">
-        <v>Fried in cold-pressed oil.</v>
-      </c>
-      <c r="L135" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>GS-1135</v>
-      </c>
-      <c r="B136" t="str">
-        <v>Handmade Garlic Murukku</v>
-      </c>
-      <c r="C136" t="str">
-        <v>Heritage Crisps &amp; Snacks</v>
-      </c>
-      <c r="D136">
-        <v>120</v>
-      </c>
-      <c r="E136">
-        <v>145</v>
-      </c>
-      <c r="F136" t="str">
-        <v>200 g</v>
-      </c>
-      <c r="G136">
-        <v>4.9</v>
-      </c>
-      <c r="H136">
-        <v>326</v>
-      </c>
-      <c r="I136" t="str">
-        <v>https://images.unsplash.com/photo-1599490659213-e2b9527bd087?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J136" t="str">
-        <v>Crispy spiral snacks infused with real crushed country garlic cloves.</v>
-      </c>
-      <c r="K136" t="str">
-        <v>Savory garlic crunch in every bite.</v>
-      </c>
-      <c r="L136" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>GS-1136</v>
-      </c>
-      <c r="B137" t="str">
-        <v>Spicy Tapioca Chips (Maravalli Kizhangu)</v>
-      </c>
-      <c r="C137" t="str">
-        <v>Heritage Crisps &amp; Snacks</v>
-      </c>
-      <c r="D137">
-        <v>115</v>
-      </c>
-      <c r="E137">
-        <v>140</v>
-      </c>
-      <c r="F137" t="str">
-        <v>200 g</v>
-      </c>
-      <c r="G137">
-        <v>4.9</v>
-      </c>
-      <c r="H137">
-        <v>370</v>
-      </c>
-      <c r="I137" t="str">
-        <v>https://images.unsplash.com/photo-1599490659213-e2b9527bd087?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J137" t="str">
-        <v>Thin wafer chips of fresh cassava root dusted with red chilli powder and salt.</v>
-      </c>
-      <c r="K137" t="str">
-        <v>Crunchy southern street delicacy.</v>
-      </c>
-      <c r="L137" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>GS-1137</v>
-      </c>
-      <c r="B138" t="str">
-        <v>Roasted Salted Peanuts (Bharuchi)</v>
-      </c>
-      <c r="C138" t="str">
-        <v>Heritage Crisps &amp; Snacks</v>
-      </c>
-      <c r="D138">
-        <v>95</v>
-      </c>
-      <c r="E138">
-        <v>120</v>
-      </c>
-      <c r="F138" t="str">
-        <v>250 g</v>
-      </c>
-      <c r="G138">
-        <v>4.6</v>
-      </c>
-      <c r="H138">
-        <v>303</v>
-      </c>
-      <c r="I138" t="str">
-        <v>https://images.unsplash.com/photo-1599490659213-e2b9527bd087?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J138" t="str">
-        <v>Clay-oven sand roasted Gujarat peanuts with red skin intact and deep crunch.</v>
-      </c>
-      <c r="K138" t="str">
-        <v>Classic tea-time healthy protein snack.</v>
-      </c>
-      <c r="L138" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>GS-1138</v>
-      </c>
-      <c r="B139" t="str">
-        <v>Sweet Jaggery Banana Chips (Sharkara Varatti)</v>
-      </c>
-      <c r="C139" t="str">
-        <v>Heritage Crisps &amp; Snacks</v>
-      </c>
-      <c r="D139">
-        <v>160</v>
-      </c>
-      <c r="E139">
-        <v>195</v>
-      </c>
-      <c r="F139" t="str">
-        <v>250 g</v>
-      </c>
-      <c r="G139">
-        <v>4.6</v>
-      </c>
-      <c r="H139">
-        <v>50</v>
-      </c>
-      <c r="I139" t="str">
-        <v>https://images.unsplash.com/photo-1599490659213-e2b9527bd087?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J139" t="str">
-        <v>Thick plantain chunks coated in ginger, cardamom, and thick palm jaggery.</v>
-      </c>
-      <c r="K139" t="str">
-        <v>Kerala festival delicacy on Vishu &amp; Onam.</v>
-      </c>
-      <c r="L139" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>GS-1139</v>
-      </c>
-      <c r="B140" t="str">
-        <v>Multi-Millet Sev (Bhavnagri Style)</v>
-      </c>
-      <c r="C140" t="str">
-        <v>Heritage Crisps &amp; Snacks</v>
-      </c>
-      <c r="D140">
-        <v>115</v>
-      </c>
-      <c r="E140">
-        <v>140</v>
-      </c>
-      <c r="F140" t="str">
-        <v>200 g</v>
-      </c>
-      <c r="G140">
-        <v>4.7</v>
-      </c>
-      <c r="H140">
-        <v>309</v>
-      </c>
-      <c r="I140" t="str">
-        <v>https://images.unsplash.com/photo-1599490659213-e2b9527bd087?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J140" t="str">
-        <v>Melt-in-mouth thick sev crafted from ragi, jowar, and gram flour with ajwain.</v>
-      </c>
-      <c r="K140" t="str">
-        <v>Wholesome gluten-conscious snack.</v>
-      </c>
-      <c r="L140" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>GS-1140</v>
-      </c>
-      <c r="B141" t="str">
-        <v>Organic Roasted Flaxseed Mukhwas</v>
-      </c>
-      <c r="C141" t="str">
-        <v>Heritage Crisps &amp; Snacks</v>
-      </c>
-      <c r="D141">
-        <v>90</v>
-      </c>
-      <c r="E141">
-        <v>115</v>
-      </c>
-      <c r="F141" t="str">
-        <v>150 g</v>
-      </c>
-      <c r="G141">
-        <v>5</v>
-      </c>
-      <c r="H141">
-        <v>121</v>
-      </c>
-      <c r="I141" t="str">
-        <v>https://images.unsplash.com/photo-1599490659213-e2b9527bd087?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J141" t="str">
-        <v>Toasted flax and sesame seeds with dry roasted fennel and lemon rock salt.</v>
-      </c>
-      <c r="K141" t="str">
-        <v>Digestive post-meal mouth freshener.</v>
-      </c>
-      <c r="L141" t="str">
-        <v>In Stock</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>GS-1141</v>
-      </c>
-      <c r="B142" t="str">
-        <v>Heritage Coconut Thattai</v>
-      </c>
-      <c r="C142" t="str">
-        <v>Heritage Crisps &amp; Snacks</v>
-      </c>
-      <c r="D142">
-        <v>125</v>
-      </c>
-      <c r="E142">
-        <v>150</v>
-      </c>
-      <c r="F142" t="str">
-        <v>200 g</v>
-      </c>
-      <c r="G142">
-        <v>4.6</v>
-      </c>
-      <c r="H142">
-        <v>62</v>
-      </c>
-      <c r="I142" t="str">
-        <v>https://images.unsplash.com/photo-1599490659213-e2b9527bd087?auto=format&amp;fit=crop&amp;w=600&amp;q=80</v>
-      </c>
-      <c r="J142" t="str">
-        <v>Crunchy disc crackers studded with Bengal gram, fresh coconut slivers, and curry leaves.</v>
-      </c>
-      <c r="K142" t="str">
-        <v>Traditional wood-pressed oil fry.</v>
-      </c>
-      <c r="L142" t="str">
         <v>In Stock</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L142"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L121"/>
   </ignoredErrors>
 </worksheet>
 </file>